--- a/optaplanner-examples/data/flightcrewscheduling/unsolved/175flights-7days-US.xlsx
+++ b/optaplanner-examples/data/flightcrewscheduling/unsolved/175flights-7days-US.xlsx
@@ -6431,7 +6431,7 @@
       <c r="I5" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="2" t="s">
         <v>120</v>
       </c>
     </row>
@@ -6454,16 +6454,16 @@
       <c r="F6" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="H6" s="3" t="s">
+      <c r="G6" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>120</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="3" t="s">
         <v>120</v>
       </c>
     </row>
@@ -6736,19 +6736,19 @@
       <c r="D15" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="2" t="s">
         <v>120</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="3" t="s">
         <v>120</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I15" s="2" t="s">
         <v>120</v>
       </c>
       <c r="J15" s="2" t="s">
@@ -6925,19 +6925,19 @@
       <c r="C21" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="2" t="s">
         <v>120</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="2" t="s">
         <v>120</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="H21" s="3" t="s">
         <v>120</v>
       </c>
       <c r="I21" s="2" t="s">
@@ -6963,16 +6963,16 @@
       <c r="E22" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="2" t="s">
         <v>120</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I22" s="3" t="s">
+      <c r="H22" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>120</v>
       </c>
       <c r="J22" s="2" t="s">
@@ -6984,7 +6984,7 @@
         <v>149</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>17</v>
@@ -6998,16 +6998,16 @@
       <c r="F23" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="2" t="s">
         <v>120</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="I23" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="J23" s="3" t="s">
+      <c r="I23" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="J23" s="2" t="s">
         <v>120</v>
       </c>
     </row>
@@ -7080,7 +7080,7 @@
         <v>152</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>18</v>
@@ -7120,7 +7120,7 @@
       <c r="D27" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="3" t="s">
         <v>120</v>
       </c>
       <c r="F27" s="3" t="s">
@@ -7129,7 +7129,7 @@
       <c r="G27" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="H27" s="3" t="s">
+      <c r="H27" s="2" t="s">
         <v>120</v>
       </c>
       <c r="I27" s="2" t="s">
@@ -7158,7 +7158,7 @@
       <c r="F28" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G28" s="2" t="s">
         <v>120</v>
       </c>
       <c r="H28" s="2" t="s">
@@ -7176,7 +7176,7 @@
         <v>155</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>17</v>
@@ -7272,7 +7272,7 @@
         <v>158</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>18</v>
@@ -7304,7 +7304,7 @@
         <v>159</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>17</v>
@@ -7341,13 +7341,13 @@
       <c r="C34" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F34" s="3" t="s">
+      <c r="D34" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>120</v>
       </c>
       <c r="G34" s="2" t="s">
@@ -7359,7 +7359,7 @@
       <c r="I34" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="J34" s="3" t="s">
+      <c r="J34" s="2" t="s">
         <v>120</v>
       </c>
     </row>
@@ -7368,7 +7368,7 @@
         <v>161</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>18</v>
@@ -7391,7 +7391,7 @@
       <c r="I35" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="J35" s="3" t="s">
+      <c r="J35" s="2" t="s">
         <v>120</v>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
       <c r="D37" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E37" s="2" t="s">
         <v>120</v>
       </c>
       <c r="F37" s="2" t="s">
@@ -7452,7 +7452,7 @@
       <c r="H37" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="I37" s="3" t="s">
+      <c r="I37" s="2" t="s">
         <v>120</v>
       </c>
       <c r="J37" s="2" t="s">
@@ -7464,7 +7464,7 @@
         <v>164</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>17</v>
@@ -7496,7 +7496,7 @@
         <v>165</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>17</v>
@@ -7542,10 +7542,10 @@
       <c r="F40" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="H40" s="3" t="s">
+      <c r="G40" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H40" s="2" t="s">
         <v>120</v>
       </c>
       <c r="I40" s="2" t="s">
@@ -7560,7 +7560,7 @@
         <v>167</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>18</v>
@@ -7592,7 +7592,7 @@
         <v>168</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>18</v>
@@ -7624,7 +7624,7 @@
         <v>169</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>17</v>
@@ -7647,7 +7647,7 @@
       <c r="I43" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="J43" s="3" t="s">
+      <c r="J43" s="2" t="s">
         <v>120</v>
       </c>
     </row>
@@ -7656,7 +7656,7 @@
         <v>170</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>17</v>
@@ -7705,7 +7705,7 @@
       <c r="G45" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="H45" s="2" t="s">
+      <c r="H45" s="3" t="s">
         <v>120</v>
       </c>
       <c r="I45" s="2" t="s">
@@ -7720,7 +7720,7 @@
         <v>172</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>18</v>
@@ -7766,16 +7766,16 @@
       <c r="F47" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G47" s="3" t="s">
+      <c r="G47" s="2" t="s">
         <v>120</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J47" s="2" t="s">
+      <c r="I47" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="J47" s="3" t="s">
         <v>120</v>
       </c>
     </row>
@@ -7821,10 +7821,10 @@
       <c r="C49" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E49" s="3" t="s">
+      <c r="D49" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>120</v>
       </c>
       <c r="F49" s="2" t="s">
@@ -7848,7 +7848,7 @@
         <v>176</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>18</v>
@@ -7929,13 +7929,13 @@
       <c r="G52" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="H52" s="3" t="s">
+      <c r="H52" s="2" t="s">
         <v>120</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="J52" s="3" t="s">
+      <c r="J52" s="2" t="s">
         <v>120</v>
       </c>
     </row>
@@ -7944,7 +7944,7 @@
         <v>179</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>17</v>
@@ -7955,7 +7955,7 @@
       <c r="E53" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F53" s="3" t="s">
+      <c r="F53" s="2" t="s">
         <v>120</v>
       </c>
       <c r="G53" s="3" t="s">
@@ -7981,10 +7981,10 @@
       <c r="C54" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E54" s="3" t="s">
+      <c r="D54" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>120</v>
       </c>
       <c r="F54" s="2" t="s">
@@ -7993,10 +7993,10 @@
       <c r="G54" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I54" s="3" t="s">
+      <c r="H54" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I54" s="2" t="s">
         <v>120</v>
       </c>
       <c r="J54" s="2" t="s">
@@ -8008,7 +8008,7 @@
         <v>181</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>18</v>
@@ -8016,16 +8016,16 @@
       <c r="D55" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E55" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F55" s="2" t="s">
+      <c r="E55" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F55" s="3" t="s">
         <v>120</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="H55" s="3" t="s">
+      <c r="H55" s="2" t="s">
         <v>120</v>
       </c>
       <c r="I55" s="2" t="s">
@@ -8063,7 +8063,7 @@
       <c r="I56" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="J56" s="2" t="s">
+      <c r="J56" s="3" t="s">
         <v>120</v>
       </c>
     </row>
@@ -8109,7 +8109,7 @@
       <c r="C58" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="D58" s="2" t="s">
         <v>120</v>
       </c>
       <c r="E58" s="2" t="s">
@@ -8118,7 +8118,7 @@
       <c r="F58" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G58" s="3" t="s">
+      <c r="G58" s="2" t="s">
         <v>120</v>
       </c>
       <c r="H58" s="2" t="s">
@@ -8185,7 +8185,7 @@
       <c r="G60" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="H60" s="2" t="s">
+      <c r="H60" s="3" t="s">
         <v>120</v>
       </c>
       <c r="I60" s="2" t="s">
@@ -8200,7 +8200,7 @@
         <v>187</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>18</v>
@@ -8252,10 +8252,10 @@
       <c r="H62" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J62" s="3" t="s">
+      <c r="I62" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="J62" s="2" t="s">
         <v>120</v>
       </c>
     </row>
@@ -8272,7 +8272,7 @@
       <c r="D63" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E63" s="2" t="s">
+      <c r="E63" s="3" t="s">
         <v>120</v>
       </c>
       <c r="F63" s="2" t="s">
@@ -8296,12 +8296,12 @@
         <v>190</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="D64" s="3" t="s">
         <v>120</v>
       </c>
       <c r="E64" s="2" t="s">
@@ -8339,16 +8339,16 @@
       <c r="E65" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F65" s="3" t="s">
+      <c r="F65" s="2" t="s">
         <v>120</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="H65" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I65" s="3" t="s">
+      <c r="H65" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I65" s="2" t="s">
         <v>120</v>
       </c>
       <c r="J65" s="2" t="s">
@@ -8392,7 +8392,7 @@
         <v>193</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>18</v>
@@ -8400,19 +8400,19 @@
       <c r="D67" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E67" s="2" t="s">
+      <c r="E67" s="3" t="s">
         <v>120</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G67" s="2" t="s">
+      <c r="G67" s="3" t="s">
         <v>120</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="I67" s="2" t="s">
+      <c r="I67" s="3" t="s">
         <v>120</v>
       </c>
       <c r="J67" s="2" t="s">
@@ -8456,7 +8456,7 @@
         <v>195</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>17</v>
@@ -8464,13 +8464,13 @@
       <c r="D69" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E69" s="3" t="s">
+      <c r="E69" s="2" t="s">
         <v>120</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G69" s="3" t="s">
+      <c r="G69" s="2" t="s">
         <v>120</v>
       </c>
       <c r="H69" s="2" t="s">
@@ -8508,7 +8508,7 @@
       <c r="H70" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="I70" s="2" t="s">
+      <c r="I70" s="3" t="s">
         <v>120</v>
       </c>
       <c r="J70" s="2" t="s">
@@ -8525,7 +8525,7 @@
       <c r="C71" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="D71" s="2" t="s">
         <v>120</v>
       </c>
       <c r="E71" s="2" t="s">
@@ -8543,7 +8543,7 @@
       <c r="I71" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="J71" s="3" t="s">
+      <c r="J71" s="2" t="s">
         <v>120</v>
       </c>
     </row>
@@ -8552,7 +8552,7 @@
         <v>198</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>18</v>
@@ -8566,7 +8566,7 @@
       <c r="F72" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G72" s="3" t="s">
+      <c r="G72" s="2" t="s">
         <v>120</v>
       </c>
       <c r="H72" s="2" t="s">
@@ -8575,7 +8575,7 @@
       <c r="I72" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="J72" s="3" t="s">
+      <c r="J72" s="2" t="s">
         <v>120</v>
       </c>
     </row>
@@ -8584,7 +8584,7 @@
         <v>199</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>17</v>
@@ -8616,7 +8616,7 @@
         <v>200</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>17</v>
@@ -8648,7 +8648,7 @@
         <v>201</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>18</v>
@@ -8712,7 +8712,7 @@
         <v>203</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>18</v>
@@ -8744,18 +8744,18 @@
         <v>204</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="D78" s="2" t="s">
         <v>120</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F78" s="3" t="s">
+      <c r="F78" s="2" t="s">
         <v>120</v>
       </c>
       <c r="G78" s="2" t="s">
@@ -8776,7 +8776,7 @@
         <v>205</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>17</v>
@@ -8808,7 +8808,7 @@
         <v>206</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>18</v>
@@ -8819,7 +8819,7 @@
       <c r="E80" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F80" s="2" t="s">
+      <c r="F80" s="3" t="s">
         <v>120</v>
       </c>
       <c r="G80" s="2" t="s">
@@ -8840,7 +8840,7 @@
         <v>207</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>18</v>
@@ -8848,7 +8848,7 @@
       <c r="D81" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E81" s="3" t="s">
+      <c r="E81" s="2" t="s">
         <v>120</v>
       </c>
       <c r="F81" s="2" t="s">
@@ -8860,7 +8860,7 @@
       <c r="H81" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="I81" s="3" t="s">
+      <c r="I81" s="2" t="s">
         <v>120</v>
       </c>
       <c r="J81" s="2" t="s">
@@ -8872,7 +8872,7 @@
         <v>208</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>18</v>
@@ -8904,7 +8904,7 @@
         <v>209</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>17</v>
@@ -8927,7 +8927,7 @@
       <c r="I83" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="J83" s="2" t="s">
+      <c r="J83" s="3" t="s">
         <v>120</v>
       </c>
     </row>
@@ -8947,13 +8947,13 @@
       <c r="E84" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F84" s="3" t="s">
+      <c r="F84" s="2" t="s">
         <v>120</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="H84" s="3" t="s">
+      <c r="H84" s="2" t="s">
         <v>120</v>
       </c>
       <c r="I84" s="2" t="s">
@@ -8968,7 +8968,7 @@
         <v>211</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>18</v>
@@ -9000,12 +9000,12 @@
         <v>212</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D86" s="2" t="s">
+      <c r="D86" s="3" t="s">
         <v>120</v>
       </c>
       <c r="E86" s="2" t="s">
@@ -9014,7 +9014,7 @@
       <c r="F86" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G86" s="3" t="s">
+      <c r="G86" s="2" t="s">
         <v>120</v>
       </c>
       <c r="H86" s="2" t="s">
@@ -9023,7 +9023,7 @@
       <c r="I86" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="J86" s="3" t="s">
+      <c r="J86" s="2" t="s">
         <v>120</v>
       </c>
     </row>
@@ -9037,7 +9037,7 @@
       <c r="C87" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D87" s="3" t="s">
+      <c r="D87" s="2" t="s">
         <v>120</v>
       </c>
       <c r="E87" s="2" t="s">
@@ -9078,7 +9078,7 @@
       <c r="F88" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G88" s="2" t="s">
+      <c r="G88" s="3" t="s">
         <v>120</v>
       </c>
       <c r="H88" s="2" t="s">
@@ -9096,7 +9096,7 @@
         <v>215</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>17</v>
@@ -9110,7 +9110,7 @@
       <c r="F89" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G89" s="2" t="s">
+      <c r="G89" s="3" t="s">
         <v>120</v>
       </c>
       <c r="H89" s="2" t="s">
@@ -9136,7 +9136,7 @@
       <c r="D90" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E90" s="3" t="s">
+      <c r="E90" s="2" t="s">
         <v>120</v>
       </c>
       <c r="F90" s="2" t="s">
@@ -9148,7 +9148,7 @@
       <c r="H90" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="I90" s="3" t="s">
+      <c r="I90" s="2" t="s">
         <v>120</v>
       </c>
       <c r="J90" s="2" t="s">
@@ -9160,7 +9160,7 @@
         <v>217</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>18</v>
@@ -9192,7 +9192,7 @@
         <v>218</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>18</v>
@@ -9215,7 +9215,7 @@
       <c r="I92" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="J92" s="2" t="s">
+      <c r="J92" s="3" t="s">
         <v>120</v>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
         <v>219</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>17</v>
@@ -9299,10 +9299,10 @@
       <c r="E95" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F95" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="G95" s="3" t="s">
+      <c r="F95" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G95" s="2" t="s">
         <v>120</v>
       </c>
       <c r="H95" s="2" t="s">
@@ -9357,7 +9357,7 @@
       <c r="C97" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D97" s="3" t="s">
+      <c r="D97" s="2" t="s">
         <v>120</v>
       </c>
       <c r="E97" s="2" t="s">
@@ -9421,7 +9421,7 @@
       <c r="C99" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D99" s="2" t="s">
+      <c r="D99" s="3" t="s">
         <v>120</v>
       </c>
       <c r="E99" s="2" t="s">
@@ -9456,7 +9456,7 @@
       <c r="D100" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E100" s="3" t="s">
+      <c r="E100" s="2" t="s">
         <v>120</v>
       </c>
       <c r="F100" s="2" t="s">
@@ -9471,7 +9471,7 @@
       <c r="I100" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="J100" s="3" t="s">
+      <c r="J100" s="2" t="s">
         <v>120</v>
       </c>
     </row>
@@ -9480,7 +9480,7 @@
         <v>227</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>18</v>
@@ -9494,13 +9494,13 @@
       <c r="F101" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G101" s="3" t="s">
+      <c r="G101" s="2" t="s">
         <v>120</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="I101" s="3" t="s">
+      <c r="I101" s="2" t="s">
         <v>120</v>
       </c>
       <c r="J101" s="2" t="s">
@@ -9512,7 +9512,7 @@
         <v>228</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>18</v>
@@ -9532,7 +9532,7 @@
       <c r="H102" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="I102" s="2" t="s">
+      <c r="I102" s="3" t="s">
         <v>120</v>
       </c>
       <c r="J102" s="2" t="s">
@@ -9544,7 +9544,7 @@
         <v>229</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>17</v>
@@ -9576,7 +9576,7 @@
         <v>230</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>17</v>
@@ -9587,7 +9587,7 @@
       <c r="E104" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F104" s="2" t="s">
+      <c r="F104" s="3" t="s">
         <v>120</v>
       </c>
       <c r="G104" s="2" t="s">
@@ -9616,7 +9616,7 @@
       <c r="D105" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E105" s="2" t="s">
+      <c r="E105" s="3" t="s">
         <v>120</v>
       </c>
       <c r="F105" s="2" t="s">
@@ -9640,7 +9640,7 @@
         <v>232</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>18</v>
@@ -9759,7 +9759,7 @@
       <c r="I109" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="J109" s="2" t="s">
+      <c r="J109" s="3" t="s">
         <v>120</v>
       </c>
     </row>
@@ -9779,7 +9779,7 @@
       <c r="E110" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F110" s="2" t="s">
+      <c r="F110" s="3" t="s">
         <v>120</v>
       </c>
       <c r="G110" s="2" t="s">
@@ -9800,7 +9800,7 @@
         <v>237</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>18</v>
@@ -9832,7 +9832,7 @@
         <v>238</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>18</v>
@@ -9896,12 +9896,12 @@
         <v>240</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D114" s="3" t="s">
+      <c r="D114" s="2" t="s">
         <v>120</v>
       </c>
       <c r="E114" s="2" t="s">
@@ -9913,7 +9913,7 @@
       <c r="G114" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="H114" s="3" t="s">
+      <c r="H114" s="2" t="s">
         <v>120</v>
       </c>
       <c r="I114" s="2" t="s">
@@ -9936,10 +9936,10 @@
       <c r="D115" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E115" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="F115" s="3" t="s">
+      <c r="E115" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="F115" s="2" t="s">
         <v>120</v>
       </c>
       <c r="G115" s="2" t="s">
@@ -9951,7 +9951,7 @@
       <c r="I115" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="J115" s="3" t="s">
+      <c r="J115" s="2" t="s">
         <v>120</v>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
         <v>242</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>18</v>
@@ -9968,7 +9968,7 @@
       <c r="D116" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E116" s="3" t="s">
+      <c r="E116" s="2" t="s">
         <v>120</v>
       </c>
       <c r="F116" s="2" t="s">
@@ -9980,7 +9980,7 @@
       <c r="H116" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="I116" s="3" t="s">
+      <c r="I116" s="2" t="s">
         <v>120</v>
       </c>
       <c r="J116" s="2" t="s">
@@ -10009,7 +10009,7 @@
       <c r="G117" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="H117" s="2" t="s">
+      <c r="H117" s="3" t="s">
         <v>120</v>
       </c>
       <c r="I117" s="2" t="s">
@@ -10038,7 +10038,7 @@
       <c r="F118" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G118" s="2" t="s">
+      <c r="G118" s="3" t="s">
         <v>120</v>
       </c>
       <c r="H118" s="2" t="s">
@@ -10088,7 +10088,7 @@
         <v>246</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>18</v>
@@ -10201,10 +10201,10 @@
       <c r="G123" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="H123" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I123" s="3" t="s">
+      <c r="H123" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I123" s="2" t="s">
         <v>120</v>
       </c>
       <c r="J123" s="2" t="s">
@@ -10285,7 +10285,7 @@
       <c r="C126" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D126" s="2" t="s">
+      <c r="D126" s="3" t="s">
         <v>120</v>
       </c>
       <c r="E126" s="2" t="s">
@@ -10332,7 +10332,7 @@
       <c r="H127" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="I127" s="2" t="s">
+      <c r="I127" s="3" t="s">
         <v>120</v>
       </c>
       <c r="J127" s="2" t="s">
@@ -10376,7 +10376,7 @@
         <v>255</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>17</v>
@@ -10384,7 +10384,7 @@
       <c r="D129" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E129" s="3" t="s">
+      <c r="E129" s="2" t="s">
         <v>120</v>
       </c>
       <c r="F129" s="2" t="s">
@@ -10399,7 +10399,7 @@
       <c r="I129" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="J129" s="3" t="s">
+      <c r="J129" s="2" t="s">
         <v>120</v>
       </c>
     </row>
@@ -10408,7 +10408,7 @@
         <v>256</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>18</v>
@@ -10477,7 +10477,7 @@
       <c r="C132" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D132" s="2" t="s">
+      <c r="D132" s="3" t="s">
         <v>120</v>
       </c>
       <c r="E132" s="2" t="s">
@@ -10504,7 +10504,7 @@
         <v>259</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>17</v>
@@ -10536,7 +10536,7 @@
         <v>260</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>17</v>
@@ -10605,13 +10605,13 @@
       <c r="C136" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D136" s="3" t="s">
+      <c r="D136" s="2" t="s">
         <v>120</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F136" s="3" t="s">
+      <c r="F136" s="2" t="s">
         <v>120</v>
       </c>
       <c r="G136" s="2" t="s">
@@ -10672,13 +10672,13 @@
       <c r="D138" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E138" s="2" t="s">
+      <c r="E138" s="3" t="s">
         <v>120</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G138" s="3" t="s">
+      <c r="G138" s="2" t="s">
         <v>120</v>
       </c>
       <c r="H138" s="2" t="s">
@@ -10687,7 +10687,7 @@
       <c r="I138" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="J138" s="3" t="s">
+      <c r="J138" s="2" t="s">
         <v>120</v>
       </c>
     </row>
@@ -10707,13 +10707,13 @@
       <c r="E139" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F139" s="3" t="s">
+      <c r="F139" s="2" t="s">
         <v>120</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="H139" s="3" t="s">
+      <c r="H139" s="2" t="s">
         <v>120</v>
       </c>
       <c r="I139" s="2" t="s">
@@ -10739,7 +10739,7 @@
       <c r="E140" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F140" s="2" t="s">
+      <c r="F140" s="3" t="s">
         <v>120</v>
       </c>
       <c r="G140" s="2" t="s">
@@ -10792,15 +10792,15 @@
         <v>268</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D142" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E142" s="3" t="s">
+      <c r="D142" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E142" s="2" t="s">
         <v>120</v>
       </c>
       <c r="F142" s="2" t="s">
@@ -10832,22 +10832,22 @@
       <c r="D143" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E143" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F143" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="G143" s="3" t="s">
+      <c r="E143" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F143" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G143" s="2" t="s">
         <v>120</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="I143" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J143" s="2" t="s">
+      <c r="I143" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="J143" s="3" t="s">
         <v>120</v>
       </c>
     </row>
@@ -10888,7 +10888,7 @@
         <v>271</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>18</v>
@@ -10902,13 +10902,13 @@
       <c r="F145" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G145" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H145" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I145" s="3" t="s">
+      <c r="G145" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I145" s="2" t="s">
         <v>120</v>
       </c>
       <c r="J145" s="2" t="s">
@@ -10920,7 +10920,7 @@
         <v>272</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>18</v>
@@ -10952,7 +10952,7 @@
         <v>273</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>18</v>
@@ -10984,7 +10984,7 @@
         <v>274</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>17</v>
@@ -11004,7 +11004,7 @@
       <c r="H148" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="I148" s="2" t="s">
+      <c r="I148" s="3" t="s">
         <v>120</v>
       </c>
       <c r="J148" s="2" t="s">
@@ -11048,7 +11048,7 @@
         <v>276</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>18</v>
@@ -11126,7 +11126,7 @@
       <c r="F152" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G152" s="3" t="s">
+      <c r="G152" s="2" t="s">
         <v>120</v>
       </c>
       <c r="H152" s="2" t="s">
@@ -11135,7 +11135,7 @@
       <c r="I152" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="J152" s="3" t="s">
+      <c r="J152" s="2" t="s">
         <v>120</v>
       </c>
     </row>
@@ -16184,7 +16184,7 @@
         <v>149</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24">
@@ -16208,7 +16208,7 @@
         <v>152</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27">
@@ -16232,7 +16232,7 @@
         <v>155</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30">
@@ -16256,7 +16256,7 @@
         <v>158</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33">
@@ -16264,7 +16264,7 @@
         <v>159</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34">
@@ -16280,7 +16280,7 @@
         <v>161</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36">
@@ -16304,7 +16304,7 @@
         <v>164</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39">
@@ -16312,7 +16312,7 @@
         <v>165</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40">
@@ -16328,7 +16328,7 @@
         <v>167</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42">
@@ -16336,7 +16336,7 @@
         <v>168</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43">
@@ -16344,7 +16344,7 @@
         <v>169</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44">
@@ -16352,7 +16352,7 @@
         <v>170</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45">
@@ -16368,7 +16368,7 @@
         <v>172</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47">
@@ -16400,7 +16400,7 @@
         <v>176</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51">
@@ -16424,7 +16424,7 @@
         <v>179</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="54">
@@ -16440,7 +16440,7 @@
         <v>181</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="56">
@@ -16488,7 +16488,7 @@
         <v>187</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62">
@@ -16512,7 +16512,7 @@
         <v>190</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="65">
@@ -16536,7 +16536,7 @@
         <v>193</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="68">
@@ -16552,7 +16552,7 @@
         <v>195</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="70">
@@ -16576,7 +16576,7 @@
         <v>198</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73">
@@ -16584,7 +16584,7 @@
         <v>199</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74">
@@ -16592,7 +16592,7 @@
         <v>200</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="75">
@@ -16600,7 +16600,7 @@
         <v>201</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="76">
@@ -16616,7 +16616,7 @@
         <v>203</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="78">
@@ -16624,7 +16624,7 @@
         <v>204</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="79">
@@ -16632,7 +16632,7 @@
         <v>205</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="80">
@@ -16640,7 +16640,7 @@
         <v>206</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81">
@@ -16648,7 +16648,7 @@
         <v>207</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="82">
@@ -16656,7 +16656,7 @@
         <v>208</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="83">
@@ -16664,7 +16664,7 @@
         <v>209</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="84">
@@ -16680,7 +16680,7 @@
         <v>211</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="86">
@@ -16688,7 +16688,7 @@
         <v>212</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="87">
@@ -16712,7 +16712,7 @@
         <v>215</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="90">
@@ -16728,7 +16728,7 @@
         <v>217</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="92">
@@ -16736,7 +16736,7 @@
         <v>218</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="93">
@@ -16744,7 +16744,7 @@
         <v>219</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="94">
@@ -16808,7 +16808,7 @@
         <v>227</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="102">
@@ -16816,7 +16816,7 @@
         <v>228</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="103">
@@ -16824,7 +16824,7 @@
         <v>229</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="104">
@@ -16832,7 +16832,7 @@
         <v>230</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="105">
@@ -16848,7 +16848,7 @@
         <v>232</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="107">
@@ -16888,7 +16888,7 @@
         <v>237</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="112">
@@ -16896,7 +16896,7 @@
         <v>238</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="113">
@@ -16912,7 +16912,7 @@
         <v>240</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="115">
@@ -16928,7 +16928,7 @@
         <v>242</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="117">
@@ -16960,7 +16960,7 @@
         <v>246</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="121">
@@ -17032,7 +17032,7 @@
         <v>255</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="130">
@@ -17040,7 +17040,7 @@
         <v>256</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="131">
@@ -17064,7 +17064,7 @@
         <v>259</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="134">
@@ -17072,7 +17072,7 @@
         <v>260</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="135">
@@ -17136,7 +17136,7 @@
         <v>268</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="143">
@@ -17160,7 +17160,7 @@
         <v>271</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="146">
@@ -17168,7 +17168,7 @@
         <v>272</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="147">
@@ -17176,7 +17176,7 @@
         <v>273</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="148">
@@ -17184,7 +17184,7 @@
         <v>274</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="149">
@@ -17200,7 +17200,7 @@
         <v>276</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="151">

--- a/optaplanner-examples/data/flightcrewscheduling/unsolved/175flights-7days-US.xlsx
+++ b/optaplanner-examples/data/flightcrewscheduling/unsolved/175flights-7days-US.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3400" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3401" uniqueCount="683">
   <si>
     <t>Schedule start UTC Date</t>
   </si>
@@ -885,6 +885,39 @@
     <t>Employee assignments</t>
   </si>
   <si>
+    <t>AB007</t>
+  </si>
+  <si>
+    <t>2018-01-01 06:08</t>
+  </si>
+  <si>
+    <t>2018-01-01 08:19</t>
+  </si>
+  <si>
+    <t>Pilot, Pilot, Flight attendant, Flight attendant, Flight attendant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">, , , , </t>
+  </si>
+  <si>
+    <t>AB024</t>
+  </si>
+  <si>
+    <t>2018-01-01 06:39</t>
+  </si>
+  <si>
+    <t>2018-01-01 10:28</t>
+  </si>
+  <si>
+    <t>AB009</t>
+  </si>
+  <si>
+    <t>2018-01-01 07:39</t>
+  </si>
+  <si>
+    <t>2018-01-01 10:47</t>
+  </si>
+  <si>
     <t>AB023</t>
   </si>
   <si>
@@ -894,10 +927,22 @@
     <t>2018-01-01 11:53</t>
   </si>
   <si>
-    <t>Pilot, Pilot, Flight attendant, Flight attendant, Flight attendant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">, , , , </t>
+    <t>AB003</t>
+  </si>
+  <si>
+    <t>2018-01-01 08:45</t>
+  </si>
+  <si>
+    <t>2018-01-01 10:33</t>
+  </si>
+  <si>
+    <t>AB020</t>
+  </si>
+  <si>
+    <t>2018-01-01 08:58</t>
+  </si>
+  <si>
+    <t>2018-01-01 13:20</t>
   </si>
   <si>
     <t>AB016</t>
@@ -909,6 +954,114 @@
     <t>2018-01-01 14:18</t>
   </si>
   <si>
+    <t>AB011</t>
+  </si>
+  <si>
+    <t>2018-01-01 09:47</t>
+  </si>
+  <si>
+    <t>2018-01-01 12:09</t>
+  </si>
+  <si>
+    <t>AB019</t>
+  </si>
+  <si>
+    <t>2018-01-01 09:53</t>
+  </si>
+  <si>
+    <t>2018-01-01 14:41</t>
+  </si>
+  <si>
+    <t>AB014</t>
+  </si>
+  <si>
+    <t>2018-01-01 10:38</t>
+  </si>
+  <si>
+    <t>2018-01-01 13:19</t>
+  </si>
+  <si>
+    <t>AB022</t>
+  </si>
+  <si>
+    <t>2018-01-01 11:18</t>
+  </si>
+  <si>
+    <t>2018-01-01 13:37</t>
+  </si>
+  <si>
+    <t>AB017</t>
+  </si>
+  <si>
+    <t>2018-01-01 11:21</t>
+  </si>
+  <si>
+    <t>2018-01-01 16:17</t>
+  </si>
+  <si>
+    <t>AB025</t>
+  </si>
+  <si>
+    <t>2018-01-01 11:33</t>
+  </si>
+  <si>
+    <t>2018-01-01 14:48</t>
+  </si>
+  <si>
+    <t>AB010</t>
+  </si>
+  <si>
+    <t>2018-01-01 11:34</t>
+  </si>
+  <si>
+    <t>2018-01-01 13:48</t>
+  </si>
+  <si>
+    <t>AB002</t>
+  </si>
+  <si>
+    <t>2018-01-01 12:06</t>
+  </si>
+  <si>
+    <t>2018-01-01 14:56</t>
+  </si>
+  <si>
+    <t>AB021</t>
+  </si>
+  <si>
+    <t>2018-01-01 12:28</t>
+  </si>
+  <si>
+    <t>2018-01-01 14:47</t>
+  </si>
+  <si>
+    <t>AB004</t>
+  </si>
+  <si>
+    <t>2018-01-01 13:29</t>
+  </si>
+  <si>
+    <t>2018-01-01 15:51</t>
+  </si>
+  <si>
+    <t>AB008</t>
+  </si>
+  <si>
+    <t>2018-01-01 13:46</t>
+  </si>
+  <si>
+    <t>2018-01-01 16:10</t>
+  </si>
+  <si>
+    <t>AB015</t>
+  </si>
+  <si>
+    <t>2018-01-01 14:33</t>
+  </si>
+  <si>
+    <t>2018-01-01 17:16</t>
+  </si>
+  <si>
     <t>AB018</t>
   </si>
   <si>
@@ -918,6 +1071,39 @@
     <t>2018-01-01 17:49</t>
   </si>
   <si>
+    <t>AB001</t>
+  </si>
+  <si>
+    <t>2018-01-01 15:42</t>
+  </si>
+  <si>
+    <t>2018-01-01 18:32</t>
+  </si>
+  <si>
+    <t>AB012</t>
+  </si>
+  <si>
+    <t>2018-01-01 17:33</t>
+  </si>
+  <si>
+    <t>2018-01-01 19:55</t>
+  </si>
+  <si>
+    <t>AB005</t>
+  </si>
+  <si>
+    <t>2018-01-01 20:35</t>
+  </si>
+  <si>
+    <t>AB006</t>
+  </si>
+  <si>
+    <t>2018-01-01 18:33</t>
+  </si>
+  <si>
+    <t>2018-01-01 20:44</t>
+  </si>
+  <si>
     <t>AB013</t>
   </si>
   <si>
@@ -927,190 +1113,22 @@
     <t>2018-01-01 21:17</t>
   </si>
   <si>
-    <t>AB003</t>
-  </si>
-  <si>
-    <t>2018-01-01 08:45</t>
-  </si>
-  <si>
-    <t>2018-01-01 10:33</t>
-  </si>
-  <si>
-    <t>AB011</t>
-  </si>
-  <si>
-    <t>2018-01-01 09:47</t>
-  </si>
-  <si>
-    <t>2018-01-01 12:09</t>
-  </si>
-  <si>
-    <t>AB021</t>
-  </si>
-  <si>
-    <t>2018-01-01 12:28</t>
-  </si>
-  <si>
-    <t>2018-01-01 14:47</t>
-  </si>
-  <si>
-    <t>AB008</t>
-  </si>
-  <si>
-    <t>2018-01-01 13:46</t>
-  </si>
-  <si>
-    <t>2018-01-01 16:10</t>
-  </si>
-  <si>
-    <t>AB001</t>
-  </si>
-  <si>
-    <t>2018-01-01 15:42</t>
-  </si>
-  <si>
-    <t>2018-01-01 18:32</t>
-  </si>
-  <si>
-    <t>AB006</t>
-  </si>
-  <si>
-    <t>2018-01-01 18:33</t>
-  </si>
-  <si>
-    <t>2018-01-01 20:44</t>
-  </si>
-  <si>
-    <t>AB020</t>
-  </si>
-  <si>
-    <t>2018-01-01 08:58</t>
-  </si>
-  <si>
-    <t>2018-01-01 13:20</t>
-  </si>
-  <si>
-    <t>AB022</t>
-  </si>
-  <si>
-    <t>2018-01-01 11:18</t>
-  </si>
-  <si>
-    <t>2018-01-01 13:37</t>
-  </si>
-  <si>
-    <t>AB007</t>
-  </si>
-  <si>
-    <t>2018-01-01 06:08</t>
-  </si>
-  <si>
-    <t>2018-01-01 08:19</t>
-  </si>
-  <si>
-    <t>AB010</t>
-  </si>
-  <si>
-    <t>2018-01-01 11:34</t>
-  </si>
-  <si>
-    <t>2018-01-01 13:48</t>
-  </si>
-  <si>
-    <t>AB009</t>
-  </si>
-  <si>
-    <t>2018-01-01 07:39</t>
-  </si>
-  <si>
-    <t>2018-01-01 10:47</t>
-  </si>
-  <si>
-    <t>AB014</t>
-  </si>
-  <si>
-    <t>2018-01-01 10:38</t>
-  </si>
-  <si>
-    <t>2018-01-01 13:19</t>
-  </si>
-  <si>
-    <t>AB005</t>
-  </si>
-  <si>
-    <t>2018-01-01 20:35</t>
-  </si>
-  <si>
-    <t>AB012</t>
-  </si>
-  <si>
-    <t>2018-01-01 17:33</t>
-  </si>
-  <si>
-    <t>2018-01-01 19:55</t>
-  </si>
-  <si>
-    <t>AB002</t>
-  </si>
-  <si>
-    <t>2018-01-01 12:06</t>
-  </si>
-  <si>
-    <t>2018-01-01 14:56</t>
-  </si>
-  <si>
-    <t>AB025</t>
-  </si>
-  <si>
-    <t>2018-01-01 11:33</t>
-  </si>
-  <si>
-    <t>2018-01-01 14:48</t>
-  </si>
-  <si>
-    <t>AB024</t>
-  </si>
-  <si>
-    <t>2018-01-01 06:39</t>
-  </si>
-  <si>
-    <t>2018-01-01 10:28</t>
-  </si>
-  <si>
-    <t>AB017</t>
-  </si>
-  <si>
-    <t>2018-01-01 11:21</t>
-  </si>
-  <si>
-    <t>2018-01-01 16:17</t>
-  </si>
-  <si>
-    <t>AB004</t>
-  </si>
-  <si>
-    <t>2018-01-01 13:29</t>
-  </si>
-  <si>
-    <t>2018-01-01 15:51</t>
-  </si>
-  <si>
-    <t>AB019</t>
-  </si>
-  <si>
-    <t>2018-01-01 09:53</t>
-  </si>
-  <si>
-    <t>2018-01-01 14:41</t>
-  </si>
-  <si>
-    <t>AB015</t>
-  </si>
-  <si>
-    <t>2018-01-01 14:33</t>
-  </si>
-  <si>
-    <t>2018-01-01 17:16</t>
+    <t>2018-01-02 06:08</t>
+  </si>
+  <si>
+    <t>2018-01-02 08:19</t>
+  </si>
+  <si>
+    <t>2018-01-02 06:39</t>
+  </si>
+  <si>
+    <t>2018-01-02 10:28</t>
+  </si>
+  <si>
+    <t>2018-01-02 07:39</t>
+  </si>
+  <si>
+    <t>2018-01-02 10:47</t>
   </si>
   <si>
     <t>2018-01-02 08:22</t>
@@ -1119,145 +1137,145 @@
     <t>2018-01-02 11:53</t>
   </si>
   <si>
+    <t>2018-01-02 08:45</t>
+  </si>
+  <si>
+    <t>2018-01-02 10:33</t>
+  </si>
+  <si>
+    <t>2018-01-02 08:58</t>
+  </si>
+  <si>
+    <t>2018-01-02 13:20</t>
+  </si>
+  <si>
     <t>2018-01-02 09:22</t>
   </si>
   <si>
     <t>2018-01-02 14:18</t>
   </si>
   <si>
+    <t>2018-01-02 09:47</t>
+  </si>
+  <si>
+    <t>2018-01-02 12:09</t>
+  </si>
+  <si>
+    <t>2018-01-02 09:53</t>
+  </si>
+  <si>
+    <t>2018-01-02 14:41</t>
+  </si>
+  <si>
+    <t>2018-01-02 10:38</t>
+  </si>
+  <si>
+    <t>2018-01-02 13:19</t>
+  </si>
+  <si>
+    <t>2018-01-02 11:18</t>
+  </si>
+  <si>
+    <t>2018-01-02 13:37</t>
+  </si>
+  <si>
+    <t>2018-01-02 11:21</t>
+  </si>
+  <si>
+    <t>2018-01-02 16:17</t>
+  </si>
+  <si>
+    <t>2018-01-02 11:33</t>
+  </si>
+  <si>
+    <t>2018-01-02 14:48</t>
+  </si>
+  <si>
+    <t>2018-01-02 11:34</t>
+  </si>
+  <si>
+    <t>2018-01-02 13:48</t>
+  </si>
+  <si>
+    <t>2018-01-02 12:06</t>
+  </si>
+  <si>
+    <t>2018-01-02 14:56</t>
+  </si>
+  <si>
+    <t>2018-01-02 12:28</t>
+  </si>
+  <si>
+    <t>2018-01-02 14:47</t>
+  </si>
+  <si>
+    <t>2018-01-02 13:29</t>
+  </si>
+  <si>
+    <t>2018-01-02 15:51</t>
+  </si>
+  <si>
+    <t>2018-01-02 13:46</t>
+  </si>
+  <si>
+    <t>2018-01-02 16:10</t>
+  </si>
+  <si>
+    <t>2018-01-02 14:33</t>
+  </si>
+  <si>
+    <t>2018-01-02 17:16</t>
+  </si>
+  <si>
     <t>2018-01-02 15:20</t>
   </si>
   <si>
     <t>2018-01-02 17:49</t>
   </si>
   <si>
+    <t>2018-01-02 15:42</t>
+  </si>
+  <si>
+    <t>2018-01-02 18:32</t>
+  </si>
+  <si>
+    <t>2018-01-02 17:33</t>
+  </si>
+  <si>
+    <t>2018-01-02 19:55</t>
+  </si>
+  <si>
+    <t>2018-01-02 20:35</t>
+  </si>
+  <si>
+    <t>2018-01-02 18:33</t>
+  </si>
+  <si>
+    <t>2018-01-02 20:44</t>
+  </si>
+  <si>
     <t>2018-01-02 19:26</t>
   </si>
   <si>
     <t>2018-01-02 21:17</t>
   </si>
   <si>
-    <t>2018-01-02 08:45</t>
-  </si>
-  <si>
-    <t>2018-01-02 10:33</t>
-  </si>
-  <si>
-    <t>2018-01-02 09:47</t>
-  </si>
-  <si>
-    <t>2018-01-02 12:09</t>
-  </si>
-  <si>
-    <t>2018-01-02 12:28</t>
-  </si>
-  <si>
-    <t>2018-01-02 14:47</t>
-  </si>
-  <si>
-    <t>2018-01-02 13:46</t>
-  </si>
-  <si>
-    <t>2018-01-02 16:10</t>
-  </si>
-  <si>
-    <t>2018-01-02 15:42</t>
-  </si>
-  <si>
-    <t>2018-01-02 18:32</t>
-  </si>
-  <si>
-    <t>2018-01-02 18:33</t>
-  </si>
-  <si>
-    <t>2018-01-02 20:44</t>
-  </si>
-  <si>
-    <t>2018-01-02 08:58</t>
-  </si>
-  <si>
-    <t>2018-01-02 13:20</t>
-  </si>
-  <si>
-    <t>2018-01-02 11:18</t>
-  </si>
-  <si>
-    <t>2018-01-02 13:37</t>
-  </si>
-  <si>
-    <t>2018-01-02 06:08</t>
-  </si>
-  <si>
-    <t>2018-01-02 08:19</t>
-  </si>
-  <si>
-    <t>2018-01-02 11:34</t>
-  </si>
-  <si>
-    <t>2018-01-02 13:48</t>
-  </si>
-  <si>
-    <t>2018-01-02 07:39</t>
-  </si>
-  <si>
-    <t>2018-01-02 10:47</t>
-  </si>
-  <si>
-    <t>2018-01-02 10:38</t>
-  </si>
-  <si>
-    <t>2018-01-02 13:19</t>
-  </si>
-  <si>
-    <t>2018-01-02 20:35</t>
-  </si>
-  <si>
-    <t>2018-01-02 17:33</t>
-  </si>
-  <si>
-    <t>2018-01-02 19:55</t>
-  </si>
-  <si>
-    <t>2018-01-02 12:06</t>
-  </si>
-  <si>
-    <t>2018-01-02 14:56</t>
-  </si>
-  <si>
-    <t>2018-01-02 11:33</t>
-  </si>
-  <si>
-    <t>2018-01-02 14:48</t>
-  </si>
-  <si>
-    <t>2018-01-02 06:39</t>
-  </si>
-  <si>
-    <t>2018-01-02 10:28</t>
-  </si>
-  <si>
-    <t>2018-01-02 11:21</t>
-  </si>
-  <si>
-    <t>2018-01-02 16:17</t>
-  </si>
-  <si>
-    <t>2018-01-02 13:29</t>
-  </si>
-  <si>
-    <t>2018-01-02 15:51</t>
-  </si>
-  <si>
-    <t>2018-01-02 09:53</t>
-  </si>
-  <si>
-    <t>2018-01-02 14:41</t>
-  </si>
-  <si>
-    <t>2018-01-02 14:33</t>
-  </si>
-  <si>
-    <t>2018-01-02 17:16</t>
+    <t>2018-01-03 06:08</t>
+  </si>
+  <si>
+    <t>2018-01-03 08:19</t>
+  </si>
+  <si>
+    <t>2018-01-03 06:39</t>
+  </si>
+  <si>
+    <t>2018-01-03 10:28</t>
+  </si>
+  <si>
+    <t>2018-01-03 07:39</t>
+  </si>
+  <si>
+    <t>2018-01-03 10:47</t>
   </si>
   <si>
     <t>2018-01-03 08:22</t>
@@ -1266,145 +1284,145 @@
     <t>2018-01-03 11:53</t>
   </si>
   <si>
+    <t>2018-01-03 08:45</t>
+  </si>
+  <si>
+    <t>2018-01-03 10:33</t>
+  </si>
+  <si>
+    <t>2018-01-03 08:58</t>
+  </si>
+  <si>
+    <t>2018-01-03 13:20</t>
+  </si>
+  <si>
     <t>2018-01-03 09:22</t>
   </si>
   <si>
     <t>2018-01-03 14:18</t>
   </si>
   <si>
+    <t>2018-01-03 09:47</t>
+  </si>
+  <si>
+    <t>2018-01-03 12:09</t>
+  </si>
+  <si>
+    <t>2018-01-03 09:53</t>
+  </si>
+  <si>
+    <t>2018-01-03 14:41</t>
+  </si>
+  <si>
+    <t>2018-01-03 10:38</t>
+  </si>
+  <si>
+    <t>2018-01-03 13:19</t>
+  </si>
+  <si>
+    <t>2018-01-03 11:18</t>
+  </si>
+  <si>
+    <t>2018-01-03 13:37</t>
+  </si>
+  <si>
+    <t>2018-01-03 11:21</t>
+  </si>
+  <si>
+    <t>2018-01-03 16:17</t>
+  </si>
+  <si>
+    <t>2018-01-03 11:33</t>
+  </si>
+  <si>
+    <t>2018-01-03 14:48</t>
+  </si>
+  <si>
+    <t>2018-01-03 11:34</t>
+  </si>
+  <si>
+    <t>2018-01-03 13:48</t>
+  </si>
+  <si>
+    <t>2018-01-03 12:06</t>
+  </si>
+  <si>
+    <t>2018-01-03 14:56</t>
+  </si>
+  <si>
+    <t>2018-01-03 12:28</t>
+  </si>
+  <si>
+    <t>2018-01-03 14:47</t>
+  </si>
+  <si>
+    <t>2018-01-03 13:29</t>
+  </si>
+  <si>
+    <t>2018-01-03 15:51</t>
+  </si>
+  <si>
+    <t>2018-01-03 13:46</t>
+  </si>
+  <si>
+    <t>2018-01-03 16:10</t>
+  </si>
+  <si>
+    <t>2018-01-03 14:33</t>
+  </si>
+  <si>
+    <t>2018-01-03 17:16</t>
+  </si>
+  <si>
     <t>2018-01-03 15:20</t>
   </si>
   <si>
     <t>2018-01-03 17:49</t>
   </si>
   <si>
+    <t>2018-01-03 15:42</t>
+  </si>
+  <si>
+    <t>2018-01-03 18:32</t>
+  </si>
+  <si>
+    <t>2018-01-03 17:33</t>
+  </si>
+  <si>
+    <t>2018-01-03 19:55</t>
+  </si>
+  <si>
+    <t>2018-01-03 20:35</t>
+  </si>
+  <si>
+    <t>2018-01-03 18:33</t>
+  </si>
+  <si>
+    <t>2018-01-03 20:44</t>
+  </si>
+  <si>
     <t>2018-01-03 19:26</t>
   </si>
   <si>
     <t>2018-01-03 21:17</t>
   </si>
   <si>
-    <t>2018-01-03 08:45</t>
-  </si>
-  <si>
-    <t>2018-01-03 10:33</t>
-  </si>
-  <si>
-    <t>2018-01-03 09:47</t>
-  </si>
-  <si>
-    <t>2018-01-03 12:09</t>
-  </si>
-  <si>
-    <t>2018-01-03 12:28</t>
-  </si>
-  <si>
-    <t>2018-01-03 14:47</t>
-  </si>
-  <si>
-    <t>2018-01-03 13:46</t>
-  </si>
-  <si>
-    <t>2018-01-03 16:10</t>
-  </si>
-  <si>
-    <t>2018-01-03 15:42</t>
-  </si>
-  <si>
-    <t>2018-01-03 18:32</t>
-  </si>
-  <si>
-    <t>2018-01-03 18:33</t>
-  </si>
-  <si>
-    <t>2018-01-03 20:44</t>
-  </si>
-  <si>
-    <t>2018-01-03 08:58</t>
-  </si>
-  <si>
-    <t>2018-01-03 13:20</t>
-  </si>
-  <si>
-    <t>2018-01-03 11:18</t>
-  </si>
-  <si>
-    <t>2018-01-03 13:37</t>
-  </si>
-  <si>
-    <t>2018-01-03 06:08</t>
-  </si>
-  <si>
-    <t>2018-01-03 08:19</t>
-  </si>
-  <si>
-    <t>2018-01-03 11:34</t>
-  </si>
-  <si>
-    <t>2018-01-03 13:48</t>
-  </si>
-  <si>
-    <t>2018-01-03 07:39</t>
-  </si>
-  <si>
-    <t>2018-01-03 10:47</t>
-  </si>
-  <si>
-    <t>2018-01-03 10:38</t>
-  </si>
-  <si>
-    <t>2018-01-03 13:19</t>
-  </si>
-  <si>
-    <t>2018-01-03 20:35</t>
-  </si>
-  <si>
-    <t>2018-01-03 17:33</t>
-  </si>
-  <si>
-    <t>2018-01-03 19:55</t>
-  </si>
-  <si>
-    <t>2018-01-03 12:06</t>
-  </si>
-  <si>
-    <t>2018-01-03 14:56</t>
-  </si>
-  <si>
-    <t>2018-01-03 11:33</t>
-  </si>
-  <si>
-    <t>2018-01-03 14:48</t>
-  </si>
-  <si>
-    <t>2018-01-03 06:39</t>
-  </si>
-  <si>
-    <t>2018-01-03 10:28</t>
-  </si>
-  <si>
-    <t>2018-01-03 11:21</t>
-  </si>
-  <si>
-    <t>2018-01-03 16:17</t>
-  </si>
-  <si>
-    <t>2018-01-03 13:29</t>
-  </si>
-  <si>
-    <t>2018-01-03 15:51</t>
-  </si>
-  <si>
-    <t>2018-01-03 09:53</t>
-  </si>
-  <si>
-    <t>2018-01-03 14:41</t>
-  </si>
-  <si>
-    <t>2018-01-03 14:33</t>
-  </si>
-  <si>
-    <t>2018-01-03 17:16</t>
+    <t>2018-01-04 06:08</t>
+  </si>
+  <si>
+    <t>2018-01-04 08:19</t>
+  </si>
+  <si>
+    <t>2018-01-04 06:39</t>
+  </si>
+  <si>
+    <t>2018-01-04 10:28</t>
+  </si>
+  <si>
+    <t>2018-01-04 07:39</t>
+  </si>
+  <si>
+    <t>2018-01-04 10:47</t>
   </si>
   <si>
     <t>2018-01-04 08:22</t>
@@ -1413,145 +1431,145 @@
     <t>2018-01-04 11:53</t>
   </si>
   <si>
+    <t>2018-01-04 08:45</t>
+  </si>
+  <si>
+    <t>2018-01-04 10:33</t>
+  </si>
+  <si>
+    <t>2018-01-04 08:58</t>
+  </si>
+  <si>
+    <t>2018-01-04 13:20</t>
+  </si>
+  <si>
     <t>2018-01-04 09:22</t>
   </si>
   <si>
     <t>2018-01-04 14:18</t>
   </si>
   <si>
+    <t>2018-01-04 09:47</t>
+  </si>
+  <si>
+    <t>2018-01-04 12:09</t>
+  </si>
+  <si>
+    <t>2018-01-04 09:53</t>
+  </si>
+  <si>
+    <t>2018-01-04 14:41</t>
+  </si>
+  <si>
+    <t>2018-01-04 10:38</t>
+  </si>
+  <si>
+    <t>2018-01-04 13:19</t>
+  </si>
+  <si>
+    <t>2018-01-04 11:18</t>
+  </si>
+  <si>
+    <t>2018-01-04 13:37</t>
+  </si>
+  <si>
+    <t>2018-01-04 11:21</t>
+  </si>
+  <si>
+    <t>2018-01-04 16:17</t>
+  </si>
+  <si>
+    <t>2018-01-04 11:33</t>
+  </si>
+  <si>
+    <t>2018-01-04 14:48</t>
+  </si>
+  <si>
+    <t>2018-01-04 11:34</t>
+  </si>
+  <si>
+    <t>2018-01-04 13:48</t>
+  </si>
+  <si>
+    <t>2018-01-04 12:06</t>
+  </si>
+  <si>
+    <t>2018-01-04 14:56</t>
+  </si>
+  <si>
+    <t>2018-01-04 12:28</t>
+  </si>
+  <si>
+    <t>2018-01-04 14:47</t>
+  </si>
+  <si>
+    <t>2018-01-04 13:29</t>
+  </si>
+  <si>
+    <t>2018-01-04 15:51</t>
+  </si>
+  <si>
+    <t>2018-01-04 13:46</t>
+  </si>
+  <si>
+    <t>2018-01-04 16:10</t>
+  </si>
+  <si>
+    <t>2018-01-04 14:33</t>
+  </si>
+  <si>
+    <t>2018-01-04 17:16</t>
+  </si>
+  <si>
     <t>2018-01-04 15:20</t>
   </si>
   <si>
     <t>2018-01-04 17:49</t>
   </si>
   <si>
+    <t>2018-01-04 15:42</t>
+  </si>
+  <si>
+    <t>2018-01-04 18:32</t>
+  </si>
+  <si>
+    <t>2018-01-04 17:33</t>
+  </si>
+  <si>
+    <t>2018-01-04 19:55</t>
+  </si>
+  <si>
+    <t>2018-01-04 20:35</t>
+  </si>
+  <si>
+    <t>2018-01-04 18:33</t>
+  </si>
+  <si>
+    <t>2018-01-04 20:44</t>
+  </si>
+  <si>
     <t>2018-01-04 19:26</t>
   </si>
   <si>
     <t>2018-01-04 21:17</t>
   </si>
   <si>
-    <t>2018-01-04 08:45</t>
-  </si>
-  <si>
-    <t>2018-01-04 10:33</t>
-  </si>
-  <si>
-    <t>2018-01-04 09:47</t>
-  </si>
-  <si>
-    <t>2018-01-04 12:09</t>
-  </si>
-  <si>
-    <t>2018-01-04 12:28</t>
-  </si>
-  <si>
-    <t>2018-01-04 14:47</t>
-  </si>
-  <si>
-    <t>2018-01-04 13:46</t>
-  </si>
-  <si>
-    <t>2018-01-04 16:10</t>
-  </si>
-  <si>
-    <t>2018-01-04 15:42</t>
-  </si>
-  <si>
-    <t>2018-01-04 18:32</t>
-  </si>
-  <si>
-    <t>2018-01-04 18:33</t>
-  </si>
-  <si>
-    <t>2018-01-04 20:44</t>
-  </si>
-  <si>
-    <t>2018-01-04 08:58</t>
-  </si>
-  <si>
-    <t>2018-01-04 13:20</t>
-  </si>
-  <si>
-    <t>2018-01-04 11:18</t>
-  </si>
-  <si>
-    <t>2018-01-04 13:37</t>
-  </si>
-  <si>
-    <t>2018-01-04 06:08</t>
-  </si>
-  <si>
-    <t>2018-01-04 08:19</t>
-  </si>
-  <si>
-    <t>2018-01-04 11:34</t>
-  </si>
-  <si>
-    <t>2018-01-04 13:48</t>
-  </si>
-  <si>
-    <t>2018-01-04 07:39</t>
-  </si>
-  <si>
-    <t>2018-01-04 10:47</t>
-  </si>
-  <si>
-    <t>2018-01-04 10:38</t>
-  </si>
-  <si>
-    <t>2018-01-04 13:19</t>
-  </si>
-  <si>
-    <t>2018-01-04 20:35</t>
-  </si>
-  <si>
-    <t>2018-01-04 17:33</t>
-  </si>
-  <si>
-    <t>2018-01-04 19:55</t>
-  </si>
-  <si>
-    <t>2018-01-04 12:06</t>
-  </si>
-  <si>
-    <t>2018-01-04 14:56</t>
-  </si>
-  <si>
-    <t>2018-01-04 11:33</t>
-  </si>
-  <si>
-    <t>2018-01-04 14:48</t>
-  </si>
-  <si>
-    <t>2018-01-04 06:39</t>
-  </si>
-  <si>
-    <t>2018-01-04 10:28</t>
-  </si>
-  <si>
-    <t>2018-01-04 11:21</t>
-  </si>
-  <si>
-    <t>2018-01-04 16:17</t>
-  </si>
-  <si>
-    <t>2018-01-04 13:29</t>
-  </si>
-  <si>
-    <t>2018-01-04 15:51</t>
-  </si>
-  <si>
-    <t>2018-01-04 09:53</t>
-  </si>
-  <si>
-    <t>2018-01-04 14:41</t>
-  </si>
-  <si>
-    <t>2018-01-04 14:33</t>
-  </si>
-  <si>
-    <t>2018-01-04 17:16</t>
+    <t>2018-01-05 06:08</t>
+  </si>
+  <si>
+    <t>2018-01-05 08:19</t>
+  </si>
+  <si>
+    <t>2018-01-05 06:39</t>
+  </si>
+  <si>
+    <t>2018-01-05 10:28</t>
+  </si>
+  <si>
+    <t>2018-01-05 07:39</t>
+  </si>
+  <si>
+    <t>2018-01-05 10:47</t>
   </si>
   <si>
     <t>2018-01-05 08:22</t>
@@ -1560,145 +1578,145 @@
     <t>2018-01-05 11:53</t>
   </si>
   <si>
+    <t>2018-01-05 08:45</t>
+  </si>
+  <si>
+    <t>2018-01-05 10:33</t>
+  </si>
+  <si>
+    <t>2018-01-05 08:58</t>
+  </si>
+  <si>
+    <t>2018-01-05 13:20</t>
+  </si>
+  <si>
     <t>2018-01-05 09:22</t>
   </si>
   <si>
     <t>2018-01-05 14:18</t>
   </si>
   <si>
+    <t>2018-01-05 09:47</t>
+  </si>
+  <si>
+    <t>2018-01-05 12:09</t>
+  </si>
+  <si>
+    <t>2018-01-05 09:53</t>
+  </si>
+  <si>
+    <t>2018-01-05 14:41</t>
+  </si>
+  <si>
+    <t>2018-01-05 10:38</t>
+  </si>
+  <si>
+    <t>2018-01-05 13:19</t>
+  </si>
+  <si>
+    <t>2018-01-05 11:18</t>
+  </si>
+  <si>
+    <t>2018-01-05 13:37</t>
+  </si>
+  <si>
+    <t>2018-01-05 11:21</t>
+  </si>
+  <si>
+    <t>2018-01-05 16:17</t>
+  </si>
+  <si>
+    <t>2018-01-05 11:33</t>
+  </si>
+  <si>
+    <t>2018-01-05 14:48</t>
+  </si>
+  <si>
+    <t>2018-01-05 11:34</t>
+  </si>
+  <si>
+    <t>2018-01-05 13:48</t>
+  </si>
+  <si>
+    <t>2018-01-05 12:06</t>
+  </si>
+  <si>
+    <t>2018-01-05 14:56</t>
+  </si>
+  <si>
+    <t>2018-01-05 12:28</t>
+  </si>
+  <si>
+    <t>2018-01-05 14:47</t>
+  </si>
+  <si>
+    <t>2018-01-05 13:29</t>
+  </si>
+  <si>
+    <t>2018-01-05 15:51</t>
+  </si>
+  <si>
+    <t>2018-01-05 13:46</t>
+  </si>
+  <si>
+    <t>2018-01-05 16:10</t>
+  </si>
+  <si>
+    <t>2018-01-05 14:33</t>
+  </si>
+  <si>
+    <t>2018-01-05 17:16</t>
+  </si>
+  <si>
     <t>2018-01-05 15:20</t>
   </si>
   <si>
     <t>2018-01-05 17:49</t>
   </si>
   <si>
+    <t>2018-01-05 15:42</t>
+  </si>
+  <si>
+    <t>2018-01-05 18:32</t>
+  </si>
+  <si>
+    <t>2018-01-05 17:33</t>
+  </si>
+  <si>
+    <t>2018-01-05 19:55</t>
+  </si>
+  <si>
+    <t>2018-01-05 20:35</t>
+  </si>
+  <si>
+    <t>2018-01-05 18:33</t>
+  </si>
+  <si>
+    <t>2018-01-05 20:44</t>
+  </si>
+  <si>
     <t>2018-01-05 19:26</t>
   </si>
   <si>
     <t>2018-01-05 21:17</t>
   </si>
   <si>
-    <t>2018-01-05 08:45</t>
-  </si>
-  <si>
-    <t>2018-01-05 10:33</t>
-  </si>
-  <si>
-    <t>2018-01-05 09:47</t>
-  </si>
-  <si>
-    <t>2018-01-05 12:09</t>
-  </si>
-  <si>
-    <t>2018-01-05 12:28</t>
-  </si>
-  <si>
-    <t>2018-01-05 14:47</t>
-  </si>
-  <si>
-    <t>2018-01-05 13:46</t>
-  </si>
-  <si>
-    <t>2018-01-05 16:10</t>
-  </si>
-  <si>
-    <t>2018-01-05 15:42</t>
-  </si>
-  <si>
-    <t>2018-01-05 18:32</t>
-  </si>
-  <si>
-    <t>2018-01-05 18:33</t>
-  </si>
-  <si>
-    <t>2018-01-05 20:44</t>
-  </si>
-  <si>
-    <t>2018-01-05 08:58</t>
-  </si>
-  <si>
-    <t>2018-01-05 13:20</t>
-  </si>
-  <si>
-    <t>2018-01-05 11:18</t>
-  </si>
-  <si>
-    <t>2018-01-05 13:37</t>
-  </si>
-  <si>
-    <t>2018-01-05 06:08</t>
-  </si>
-  <si>
-    <t>2018-01-05 08:19</t>
-  </si>
-  <si>
-    <t>2018-01-05 11:34</t>
-  </si>
-  <si>
-    <t>2018-01-05 13:48</t>
-  </si>
-  <si>
-    <t>2018-01-05 07:39</t>
-  </si>
-  <si>
-    <t>2018-01-05 10:47</t>
-  </si>
-  <si>
-    <t>2018-01-05 10:38</t>
-  </si>
-  <si>
-    <t>2018-01-05 13:19</t>
-  </si>
-  <si>
-    <t>2018-01-05 20:35</t>
-  </si>
-  <si>
-    <t>2018-01-05 17:33</t>
-  </si>
-  <si>
-    <t>2018-01-05 19:55</t>
-  </si>
-  <si>
-    <t>2018-01-05 12:06</t>
-  </si>
-  <si>
-    <t>2018-01-05 14:56</t>
-  </si>
-  <si>
-    <t>2018-01-05 11:33</t>
-  </si>
-  <si>
-    <t>2018-01-05 14:48</t>
-  </si>
-  <si>
-    <t>2018-01-05 06:39</t>
-  </si>
-  <si>
-    <t>2018-01-05 10:28</t>
-  </si>
-  <si>
-    <t>2018-01-05 11:21</t>
-  </si>
-  <si>
-    <t>2018-01-05 16:17</t>
-  </si>
-  <si>
-    <t>2018-01-05 13:29</t>
-  </si>
-  <si>
-    <t>2018-01-05 15:51</t>
-  </si>
-  <si>
-    <t>2018-01-05 09:53</t>
-  </si>
-  <si>
-    <t>2018-01-05 14:41</t>
-  </si>
-  <si>
-    <t>2018-01-05 14:33</t>
-  </si>
-  <si>
-    <t>2018-01-05 17:16</t>
+    <t>2018-01-06 06:08</t>
+  </si>
+  <si>
+    <t>2018-01-06 08:19</t>
+  </si>
+  <si>
+    <t>2018-01-06 06:39</t>
+  </si>
+  <si>
+    <t>2018-01-06 10:28</t>
+  </si>
+  <si>
+    <t>2018-01-06 07:39</t>
+  </si>
+  <si>
+    <t>2018-01-06 10:47</t>
   </si>
   <si>
     <t>2018-01-06 08:22</t>
@@ -1707,145 +1725,145 @@
     <t>2018-01-06 11:53</t>
   </si>
   <si>
+    <t>2018-01-06 08:45</t>
+  </si>
+  <si>
+    <t>2018-01-06 10:33</t>
+  </si>
+  <si>
+    <t>2018-01-06 08:58</t>
+  </si>
+  <si>
+    <t>2018-01-06 13:20</t>
+  </si>
+  <si>
     <t>2018-01-06 09:22</t>
   </si>
   <si>
     <t>2018-01-06 14:18</t>
   </si>
   <si>
+    <t>2018-01-06 09:47</t>
+  </si>
+  <si>
+    <t>2018-01-06 12:09</t>
+  </si>
+  <si>
+    <t>2018-01-06 09:53</t>
+  </si>
+  <si>
+    <t>2018-01-06 14:41</t>
+  </si>
+  <si>
+    <t>2018-01-06 10:38</t>
+  </si>
+  <si>
+    <t>2018-01-06 13:19</t>
+  </si>
+  <si>
+    <t>2018-01-06 11:18</t>
+  </si>
+  <si>
+    <t>2018-01-06 13:37</t>
+  </si>
+  <si>
+    <t>2018-01-06 11:21</t>
+  </si>
+  <si>
+    <t>2018-01-06 16:17</t>
+  </si>
+  <si>
+    <t>2018-01-06 11:33</t>
+  </si>
+  <si>
+    <t>2018-01-06 14:48</t>
+  </si>
+  <si>
+    <t>2018-01-06 11:34</t>
+  </si>
+  <si>
+    <t>2018-01-06 13:48</t>
+  </si>
+  <si>
+    <t>2018-01-06 12:06</t>
+  </si>
+  <si>
+    <t>2018-01-06 14:56</t>
+  </si>
+  <si>
+    <t>2018-01-06 12:28</t>
+  </si>
+  <si>
+    <t>2018-01-06 14:47</t>
+  </si>
+  <si>
+    <t>2018-01-06 13:29</t>
+  </si>
+  <si>
+    <t>2018-01-06 15:51</t>
+  </si>
+  <si>
+    <t>2018-01-06 13:46</t>
+  </si>
+  <si>
+    <t>2018-01-06 16:10</t>
+  </si>
+  <si>
+    <t>2018-01-06 14:33</t>
+  </si>
+  <si>
+    <t>2018-01-06 17:16</t>
+  </si>
+  <si>
     <t>2018-01-06 15:20</t>
   </si>
   <si>
     <t>2018-01-06 17:49</t>
   </si>
   <si>
+    <t>2018-01-06 15:42</t>
+  </si>
+  <si>
+    <t>2018-01-06 18:32</t>
+  </si>
+  <si>
+    <t>2018-01-06 17:33</t>
+  </si>
+  <si>
+    <t>2018-01-06 19:55</t>
+  </si>
+  <si>
+    <t>2018-01-06 20:35</t>
+  </si>
+  <si>
+    <t>2018-01-06 18:33</t>
+  </si>
+  <si>
+    <t>2018-01-06 20:44</t>
+  </si>
+  <si>
     <t>2018-01-06 19:26</t>
   </si>
   <si>
     <t>2018-01-06 21:17</t>
   </si>
   <si>
-    <t>2018-01-06 08:45</t>
-  </si>
-  <si>
-    <t>2018-01-06 10:33</t>
-  </si>
-  <si>
-    <t>2018-01-06 09:47</t>
-  </si>
-  <si>
-    <t>2018-01-06 12:09</t>
-  </si>
-  <si>
-    <t>2018-01-06 12:28</t>
-  </si>
-  <si>
-    <t>2018-01-06 14:47</t>
-  </si>
-  <si>
-    <t>2018-01-06 13:46</t>
-  </si>
-  <si>
-    <t>2018-01-06 16:10</t>
-  </si>
-  <si>
-    <t>2018-01-06 15:42</t>
-  </si>
-  <si>
-    <t>2018-01-06 18:32</t>
-  </si>
-  <si>
-    <t>2018-01-06 18:33</t>
-  </si>
-  <si>
-    <t>2018-01-06 20:44</t>
-  </si>
-  <si>
-    <t>2018-01-06 08:58</t>
-  </si>
-  <si>
-    <t>2018-01-06 13:20</t>
-  </si>
-  <si>
-    <t>2018-01-06 11:18</t>
-  </si>
-  <si>
-    <t>2018-01-06 13:37</t>
-  </si>
-  <si>
-    <t>2018-01-06 06:08</t>
-  </si>
-  <si>
-    <t>2018-01-06 08:19</t>
-  </si>
-  <si>
-    <t>2018-01-06 11:34</t>
-  </si>
-  <si>
-    <t>2018-01-06 13:48</t>
-  </si>
-  <si>
-    <t>2018-01-06 07:39</t>
-  </si>
-  <si>
-    <t>2018-01-06 10:47</t>
-  </si>
-  <si>
-    <t>2018-01-06 10:38</t>
-  </si>
-  <si>
-    <t>2018-01-06 13:19</t>
-  </si>
-  <si>
-    <t>2018-01-06 20:35</t>
-  </si>
-  <si>
-    <t>2018-01-06 17:33</t>
-  </si>
-  <si>
-    <t>2018-01-06 19:55</t>
-  </si>
-  <si>
-    <t>2018-01-06 12:06</t>
-  </si>
-  <si>
-    <t>2018-01-06 14:56</t>
-  </si>
-  <si>
-    <t>2018-01-06 11:33</t>
-  </si>
-  <si>
-    <t>2018-01-06 14:48</t>
-  </si>
-  <si>
-    <t>2018-01-06 06:39</t>
-  </si>
-  <si>
-    <t>2018-01-06 10:28</t>
-  </si>
-  <si>
-    <t>2018-01-06 11:21</t>
-  </si>
-  <si>
-    <t>2018-01-06 16:17</t>
-  </si>
-  <si>
-    <t>2018-01-06 13:29</t>
-  </si>
-  <si>
-    <t>2018-01-06 15:51</t>
-  </si>
-  <si>
-    <t>2018-01-06 09:53</t>
-  </si>
-  <si>
-    <t>2018-01-06 14:41</t>
-  </si>
-  <si>
-    <t>2018-01-06 14:33</t>
-  </si>
-  <si>
-    <t>2018-01-06 17:16</t>
+    <t>2018-01-07 06:08</t>
+  </si>
+  <si>
+    <t>2018-01-07 08:19</t>
+  </si>
+  <si>
+    <t>2018-01-07 06:39</t>
+  </si>
+  <si>
+    <t>2018-01-07 10:28</t>
+  </si>
+  <si>
+    <t>2018-01-07 07:39</t>
+  </si>
+  <si>
+    <t>2018-01-07 10:47</t>
   </si>
   <si>
     <t>2018-01-07 08:22</t>
@@ -1854,147 +1872,129 @@
     <t>2018-01-07 11:53</t>
   </si>
   <si>
+    <t>2018-01-07 08:45</t>
+  </si>
+  <si>
+    <t>2018-01-07 10:33</t>
+  </si>
+  <si>
+    <t>2018-01-07 08:58</t>
+  </si>
+  <si>
+    <t>2018-01-07 13:20</t>
+  </si>
+  <si>
     <t>2018-01-07 09:22</t>
   </si>
   <si>
     <t>2018-01-07 14:18</t>
   </si>
   <si>
+    <t>2018-01-07 09:47</t>
+  </si>
+  <si>
+    <t>2018-01-07 12:09</t>
+  </si>
+  <si>
+    <t>2018-01-07 09:53</t>
+  </si>
+  <si>
+    <t>2018-01-07 14:41</t>
+  </si>
+  <si>
+    <t>2018-01-07 10:38</t>
+  </si>
+  <si>
+    <t>2018-01-07 13:19</t>
+  </si>
+  <si>
+    <t>2018-01-07 11:18</t>
+  </si>
+  <si>
+    <t>2018-01-07 13:37</t>
+  </si>
+  <si>
+    <t>2018-01-07 11:21</t>
+  </si>
+  <si>
+    <t>2018-01-07 16:17</t>
+  </si>
+  <si>
+    <t>2018-01-07 11:33</t>
+  </si>
+  <si>
+    <t>2018-01-07 14:48</t>
+  </si>
+  <si>
+    <t>2018-01-07 11:34</t>
+  </si>
+  <si>
+    <t>2018-01-07 13:48</t>
+  </si>
+  <si>
+    <t>2018-01-07 12:06</t>
+  </si>
+  <si>
+    <t>2018-01-07 14:56</t>
+  </si>
+  <si>
+    <t>2018-01-07 12:28</t>
+  </si>
+  <si>
+    <t>2018-01-07 14:47</t>
+  </si>
+  <si>
+    <t>2018-01-07 13:29</t>
+  </si>
+  <si>
+    <t>2018-01-07 15:51</t>
+  </si>
+  <si>
+    <t>2018-01-07 13:46</t>
+  </si>
+  <si>
+    <t>2018-01-07 16:10</t>
+  </si>
+  <si>
+    <t>2018-01-07 14:33</t>
+  </si>
+  <si>
+    <t>2018-01-07 17:16</t>
+  </si>
+  <si>
     <t>2018-01-07 15:20</t>
   </si>
   <si>
     <t>2018-01-07 17:49</t>
   </si>
   <si>
+    <t>2018-01-07 15:42</t>
+  </si>
+  <si>
+    <t>2018-01-07 18:32</t>
+  </si>
+  <si>
+    <t>2018-01-07 17:33</t>
+  </si>
+  <si>
+    <t>2018-01-07 19:55</t>
+  </si>
+  <si>
+    <t>2018-01-07 20:35</t>
+  </si>
+  <si>
+    <t>2018-01-07 18:33</t>
+  </si>
+  <si>
+    <t>2018-01-07 20:44</t>
+  </si>
+  <si>
     <t>2018-01-07 19:26</t>
   </si>
   <si>
     <t>2018-01-07 21:17</t>
   </si>
   <si>
-    <t>2018-01-07 08:45</t>
-  </si>
-  <si>
-    <t>2018-01-07 10:33</t>
-  </si>
-  <si>
-    <t>2018-01-07 09:47</t>
-  </si>
-  <si>
-    <t>2018-01-07 12:09</t>
-  </si>
-  <si>
-    <t>2018-01-07 12:28</t>
-  </si>
-  <si>
-    <t>2018-01-07 14:47</t>
-  </si>
-  <si>
-    <t>2018-01-07 13:46</t>
-  </si>
-  <si>
-    <t>2018-01-07 16:10</t>
-  </si>
-  <si>
-    <t>2018-01-07 15:42</t>
-  </si>
-  <si>
-    <t>2018-01-07 18:32</t>
-  </si>
-  <si>
-    <t>2018-01-07 18:33</t>
-  </si>
-  <si>
-    <t>2018-01-07 20:44</t>
-  </si>
-  <si>
-    <t>2018-01-07 08:58</t>
-  </si>
-  <si>
-    <t>2018-01-07 13:20</t>
-  </si>
-  <si>
-    <t>2018-01-07 11:18</t>
-  </si>
-  <si>
-    <t>2018-01-07 13:37</t>
-  </si>
-  <si>
-    <t>2018-01-07 06:08</t>
-  </si>
-  <si>
-    <t>2018-01-07 08:19</t>
-  </si>
-  <si>
-    <t>2018-01-07 11:34</t>
-  </si>
-  <si>
-    <t>2018-01-07 13:48</t>
-  </si>
-  <si>
-    <t>2018-01-07 07:39</t>
-  </si>
-  <si>
-    <t>2018-01-07 10:47</t>
-  </si>
-  <si>
-    <t>2018-01-07 10:38</t>
-  </si>
-  <si>
-    <t>2018-01-07 13:19</t>
-  </si>
-  <si>
-    <t>2018-01-07 20:35</t>
-  </si>
-  <si>
-    <t>2018-01-07 17:33</t>
-  </si>
-  <si>
-    <t>2018-01-07 19:55</t>
-  </si>
-  <si>
-    <t>2018-01-07 12:06</t>
-  </si>
-  <si>
-    <t>2018-01-07 14:56</t>
-  </si>
-  <si>
-    <t>2018-01-07 11:33</t>
-  </si>
-  <si>
-    <t>2018-01-07 14:48</t>
-  </si>
-  <si>
-    <t>2018-01-07 06:39</t>
-  </si>
-  <si>
-    <t>2018-01-07 10:28</t>
-  </si>
-  <si>
-    <t>2018-01-07 11:21</t>
-  </si>
-  <si>
-    <t>2018-01-07 16:17</t>
-  </si>
-  <si>
-    <t>2018-01-07 13:29</t>
-  </si>
-  <si>
-    <t>2018-01-07 15:51</t>
-  </si>
-  <si>
-    <t>2018-01-07 09:53</t>
-  </si>
-  <si>
-    <t>2018-01-07 14:41</t>
-  </si>
-  <si>
-    <t>2018-01-07 14:33</t>
-  </si>
-  <si>
-    <t>2018-01-07 17:16</t>
-  </si>
-  <si>
     <t>Employee name</t>
   </si>
   <si>
@@ -2052,19 +2052,22 @@
     <t>-875init</t>
   </si>
   <si>
-    <t>Constraint match</t>
+    <t>Constraint name</t>
+  </si>
+  <si>
+    <t>Constraint weight</t>
+  </si>
+  <si>
+    <t>Match count</t>
   </si>
   <si>
     <t>Match score</t>
   </si>
   <si>
-    <t>Total score</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    </t>
+    <t>Justifications</t>
+  </si>
+  <si>
+    <t>Unassigned variables</t>
   </si>
 </sst>
 </file>
@@ -2086,7 +2089,7 @@
       <b val="true"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2095,6 +2098,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="BABDB6"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -2121,6 +2129,16 @@
         <fgColor rgb="FCAF3E"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FCE94F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -2134,30 +2152,42 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="true" applyFont="true">
       <alignment wrapText="true" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment wrapText="true" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+      <alignment wrapText="true" vertical="center" horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment wrapText="true" vertical="center" horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment wrapText="true" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment wrapText="true" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment wrapText="true" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment wrapText="true" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment wrapText="true" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment wrapText="true" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2198,12 +2228,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="44.640625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="15.99609375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="114.34375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="44.390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="14.91015625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="113.4453125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2298,10 +2328,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="15.36328125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="14.7265625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2327,13 +2357,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="14.0859375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="24.2734375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.51171875" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="12.30078125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="13.5625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="23.42578125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="9.83984375" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="11.4765625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3030,58 +3060,58 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:AW50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="14.46875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="13.05078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="8.4296875" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="10.59375" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="11.9921875" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="7.66015625" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="8.9140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="6.5546875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.6328125" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="7.8046875" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="5.99609375" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="10.88671875" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="12.21484375" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="11.734375" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="7.7578125" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="9.59375" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="12.75" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="8.51953125" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="10.15625" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.47265625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="7.89453125" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="7.91796875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="8.0859375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="13.41796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="7.46484375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="7.53125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="11.3359375" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="8.6484375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="8.33984375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="8.82421875" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="7.7890625" customWidth="true" bestFit="true"/>
-    <col min="32" max="32" width="9.33984375" customWidth="true" bestFit="true"/>
-    <col min="33" max="33" width="7.41796875" customWidth="true" bestFit="true"/>
-    <col min="34" max="34" width="10.15234375" customWidth="true" bestFit="true"/>
-    <col min="35" max="35" width="14.46875" customWidth="true" bestFit="true"/>
-    <col min="36" max="36" width="6.6171875" customWidth="true" bestFit="true"/>
-    <col min="37" max="37" width="10.6953125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="11.26953125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="9.71875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="6.54296875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="9.41796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="6.9296875" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="13.16796875" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="11.36328125" customWidth="true" bestFit="true"/>
-    <col min="45" max="45" width="10.26953125" customWidth="true" bestFit="true"/>
-    <col min="46" max="46" width="8.72265625" customWidth="true" bestFit="true"/>
-    <col min="47" max="47" width="10.91796875" customWidth="true" bestFit="true"/>
-    <col min="48" max="48" width="9.0234375" customWidth="true" bestFit="true"/>
-    <col min="49" max="49" width="10.125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="14.3046875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="12.83203125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="8.37890625" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="10.4375" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="11.94140625" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="7.5859375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="8.90625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="6.47265625" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.65234375" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="7.57421875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="5.98828125" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="11.0078125" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="12.30859375" customWidth="true" bestFit="true"/>
+    <col min="14" max="14" width="11.546875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="7.65625" customWidth="true" bestFit="true"/>
+    <col min="16" max="16" width="9.5390625" customWidth="true" bestFit="true"/>
+    <col min="17" max="17" width="12.734375" customWidth="true" bestFit="true"/>
+    <col min="18" max="18" width="8.55078125" customWidth="true" bestFit="true"/>
+    <col min="19" max="19" width="10.05859375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.44140625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="8.15234375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="7.796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="7.92578125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="13.171875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="7.421875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="7.578125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="11.359375" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="8.69140625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="8.265625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="8.73828125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="7.82421875" customWidth="true" bestFit="true"/>
+    <col min="32" max="32" width="9.375" customWidth="true" bestFit="true"/>
+    <col min="33" max="33" width="7.2265625" customWidth="true" bestFit="true"/>
+    <col min="34" max="34" width="10.19921875" customWidth="true" bestFit="true"/>
+    <col min="35" max="35" width="14.3046875" customWidth="true" bestFit="true"/>
+    <col min="36" max="36" width="6.55859375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="10.984375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="11.17578125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="9.69140625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="6.5234375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="9.34765625" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="6.80859375" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="13.05859375" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="11.0546875" customWidth="true" bestFit="true"/>
+    <col min="45" max="45" width="10.18359375" customWidth="true" bestFit="true"/>
+    <col min="46" max="46" width="8.6015625" customWidth="true" bestFit="true"/>
+    <col min="47" max="47" width="10.953125" customWidth="true" bestFit="true"/>
+    <col min="48" max="48" width="8.828125" customWidth="true" bestFit="true"/>
+    <col min="49" max="49" width="10.0703125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6291,7 +6321,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="1">
     <mergeCell ref="A1:U1"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -6301,19 +6331,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:J152"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="14.765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="13.3359375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="15.36328125" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="16.10546875" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="15.1953125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="16.1015625" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="15.26953125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.15234375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="14.70703125" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="15.21875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="14.12890625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="13.25390625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="14.7265625" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="15.7109375" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="14.9921875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="15.671875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="15.09375" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.98828125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="14.50390625" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="15.078125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6436,7 +6466,7 @@
       <c r="C5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="5" t="s">
         <v>122</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -6486,7 +6516,7 @@
       <c r="I6" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="5" t="s">
         <v>122</v>
       </c>
     </row>
@@ -6765,7 +6795,7 @@
       <c r="F15" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="5" t="s">
         <v>122</v>
       </c>
       <c r="H15" s="2" t="s">
@@ -6960,7 +6990,7 @@
       <c r="G21" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="H21" s="5" t="s">
         <v>122</v>
       </c>
       <c r="I21" s="2" t="s">
@@ -6983,7 +7013,7 @@
       <c r="D22" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="5" t="s">
         <v>122</v>
       </c>
       <c r="F22" s="2" t="s">
@@ -7027,7 +7057,7 @@
       <c r="H23" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="I23" s="5" t="s">
         <v>122</v>
       </c>
       <c r="J23" s="2" t="s">
@@ -7143,10 +7173,10 @@
       <c r="D27" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="F27" s="3" t="s">
+      <c r="E27" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F27" s="5" t="s">
         <v>122</v>
       </c>
       <c r="G27" s="2" t="s">
@@ -7187,7 +7217,7 @@
       <c r="H28" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="I28" s="3" t="s">
+      <c r="I28" s="5" t="s">
         <v>122</v>
       </c>
       <c r="J28" s="2" t="s">
@@ -7396,7 +7426,7 @@
       <c r="C35" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="5" t="s">
         <v>122</v>
       </c>
       <c r="E35" s="2" t="s">
@@ -7658,7 +7688,7 @@
       <c r="E43" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="F43" s="3" t="s">
+      <c r="F43" s="5" t="s">
         <v>122</v>
       </c>
       <c r="G43" s="2" t="s">
@@ -7728,7 +7758,7 @@
       <c r="G45" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="H45" s="3" t="s">
+      <c r="H45" s="5" t="s">
         <v>122</v>
       </c>
       <c r="I45" s="2" t="s">
@@ -7798,7 +7828,7 @@
       <c r="I47" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="J47" s="3" t="s">
+      <c r="J47" s="5" t="s">
         <v>122</v>
       </c>
     </row>
@@ -7981,7 +8011,7 @@
       <c r="F53" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="G53" s="3" t="s">
+      <c r="G53" s="5" t="s">
         <v>122</v>
       </c>
       <c r="H53" s="2" t="s">
@@ -8042,7 +8072,7 @@
       <c r="E55" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="F55" s="3" t="s">
+      <c r="F55" s="5" t="s">
         <v>122</v>
       </c>
       <c r="G55" s="2" t="s">
@@ -8086,7 +8116,7 @@
       <c r="I56" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="J56" s="3" t="s">
+      <c r="J56" s="5" t="s">
         <v>122</v>
       </c>
     </row>
@@ -8208,7 +8238,7 @@
       <c r="G60" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="H60" s="3" t="s">
+      <c r="H60" s="5" t="s">
         <v>122</v>
       </c>
       <c r="I60" s="2" t="s">
@@ -8295,7 +8325,7 @@
       <c r="D63" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="E63" s="3" t="s">
+      <c r="E63" s="5" t="s">
         <v>122</v>
       </c>
       <c r="F63" s="2" t="s">
@@ -8324,7 +8354,7 @@
       <c r="C64" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="D64" s="5" t="s">
         <v>122</v>
       </c>
       <c r="E64" s="2" t="s">
@@ -8423,19 +8453,19 @@
       <c r="D67" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="E67" s="3" t="s">
+      <c r="E67" s="5" t="s">
         <v>122</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="G67" s="3" t="s">
+      <c r="G67" s="5" t="s">
         <v>122</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="I67" s="3" t="s">
+      <c r="I67" s="5" t="s">
         <v>122</v>
       </c>
       <c r="J67" s="2" t="s">
@@ -8531,7 +8561,7 @@
       <c r="H70" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="I70" s="3" t="s">
+      <c r="I70" s="5" t="s">
         <v>122</v>
       </c>
       <c r="J70" s="2" t="s">
@@ -8842,7 +8872,7 @@
       <c r="E80" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="F80" s="3" t="s">
+      <c r="F80" s="5" t="s">
         <v>122</v>
       </c>
       <c r="G80" s="2" t="s">
@@ -8950,7 +8980,7 @@
       <c r="I83" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="J83" s="3" t="s">
+      <c r="J83" s="5" t="s">
         <v>122</v>
       </c>
     </row>
@@ -9028,7 +9058,7 @@
       <c r="C86" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D86" s="3" t="s">
+      <c r="D86" s="5" t="s">
         <v>122</v>
       </c>
       <c r="E86" s="2" t="s">
@@ -9072,7 +9102,7 @@
       <c r="G87" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="H87" s="3" t="s">
+      <c r="H87" s="5" t="s">
         <v>122</v>
       </c>
       <c r="I87" s="2" t="s">
@@ -9101,7 +9131,7 @@
       <c r="F88" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="G88" s="3" t="s">
+      <c r="G88" s="5" t="s">
         <v>122</v>
       </c>
       <c r="H88" s="2" t="s">
@@ -9133,7 +9163,7 @@
       <c r="F89" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="G89" s="3" t="s">
+      <c r="G89" s="5" t="s">
         <v>122</v>
       </c>
       <c r="H89" s="2" t="s">
@@ -9238,7 +9268,7 @@
       <c r="I92" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="J92" s="3" t="s">
+      <c r="J92" s="5" t="s">
         <v>122</v>
       </c>
     </row>
@@ -9392,7 +9422,7 @@
       <c r="G97" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="H97" s="3" t="s">
+      <c r="H97" s="5" t="s">
         <v>122</v>
       </c>
       <c r="I97" s="2" t="s">
@@ -9444,7 +9474,7 @@
       <c r="C99" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D99" s="3" t="s">
+      <c r="D99" s="5" t="s">
         <v>122</v>
       </c>
       <c r="E99" s="2" t="s">
@@ -9555,7 +9585,7 @@
       <c r="H102" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="I102" s="3" t="s">
+      <c r="I102" s="5" t="s">
         <v>122</v>
       </c>
       <c r="J102" s="2" t="s">
@@ -9610,7 +9640,7 @@
       <c r="E104" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="F104" s="3" t="s">
+      <c r="F104" s="5" t="s">
         <v>122</v>
       </c>
       <c r="G104" s="2" t="s">
@@ -9639,7 +9669,7 @@
       <c r="D105" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="E105" s="3" t="s">
+      <c r="E105" s="5" t="s">
         <v>122</v>
       </c>
       <c r="F105" s="2" t="s">
@@ -9782,7 +9812,7 @@
       <c r="I109" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="J109" s="3" t="s">
+      <c r="J109" s="5" t="s">
         <v>122</v>
       </c>
     </row>
@@ -9802,7 +9832,7 @@
       <c r="E110" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="F110" s="3" t="s">
+      <c r="F110" s="5" t="s">
         <v>122</v>
       </c>
       <c r="G110" s="2" t="s">
@@ -9959,7 +9989,7 @@
       <c r="D115" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="E115" s="3" t="s">
+      <c r="E115" s="5" t="s">
         <v>122</v>
       </c>
       <c r="F115" s="2" t="s">
@@ -10032,7 +10062,7 @@
       <c r="G117" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="H117" s="3" t="s">
+      <c r="H117" s="5" t="s">
         <v>122</v>
       </c>
       <c r="I117" s="2" t="s">
@@ -10061,7 +10091,7 @@
       <c r="F118" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="G118" s="3" t="s">
+      <c r="G118" s="5" t="s">
         <v>122</v>
       </c>
       <c r="H118" s="2" t="s">
@@ -10308,7 +10338,7 @@
       <c r="C126" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D126" s="3" t="s">
+      <c r="D126" s="5" t="s">
         <v>122</v>
       </c>
       <c r="E126" s="2" t="s">
@@ -10355,7 +10385,7 @@
       <c r="H127" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="I127" s="3" t="s">
+      <c r="I127" s="5" t="s">
         <v>122</v>
       </c>
       <c r="J127" s="2" t="s">
@@ -10500,7 +10530,7 @@
       <c r="C132" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D132" s="3" t="s">
+      <c r="D132" s="5" t="s">
         <v>122</v>
       </c>
       <c r="E132" s="2" t="s">
@@ -10695,7 +10725,7 @@
       <c r="D138" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="E138" s="3" t="s">
+      <c r="E138" s="5" t="s">
         <v>122</v>
       </c>
       <c r="F138" s="2" t="s">
@@ -10762,7 +10792,7 @@
       <c r="E140" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="F140" s="3" t="s">
+      <c r="F140" s="5" t="s">
         <v>122</v>
       </c>
       <c r="G140" s="2" t="s">
@@ -10870,7 +10900,7 @@
       <c r="I143" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="J143" s="3" t="s">
+      <c r="J143" s="5" t="s">
         <v>122</v>
       </c>
     </row>
@@ -10925,7 +10955,7 @@
       <c r="F145" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="G145" s="3" t="s">
+      <c r="G145" s="5" t="s">
         <v>122</v>
       </c>
       <c r="H145" s="2" t="s">
@@ -11027,7 +11057,7 @@
       <c r="H148" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="I148" s="3" t="s">
+      <c r="I148" s="5" t="s">
         <v>122</v>
       </c>
       <c r="J148" s="2" t="s">
@@ -11170,16 +11200,16 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:G176"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="13.84765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="22.1328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="23.94921875" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="18.86328125" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="20.6796875" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="56.2890625" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="21.8984375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="13.8984375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="22.05078125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="23.71484375" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="18.65625" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="20.3203125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="53.78125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="21.96484375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11210,13 +11240,13 @@
         <v>288</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>289</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>290</v>
@@ -11233,13 +11263,13 @@
         <v>293</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>294</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>295</v>
@@ -11256,13 +11286,13 @@
         <v>296</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>297</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>110</v>
+        <v>54</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>298</v>
@@ -11285,7 +11315,7 @@
         <v>300</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>301</v>
@@ -11325,13 +11355,13 @@
         <v>305</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>306</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>307</v>
@@ -11348,13 +11378,13 @@
         <v>308</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>309</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>310</v>
@@ -11377,7 +11407,7 @@
         <v>312</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>313</v>
@@ -11394,13 +11424,13 @@
         <v>314</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>315</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>316</v>
@@ -11417,13 +11447,13 @@
         <v>317</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>318</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>46</v>
+        <v>116</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>319</v>
@@ -11440,13 +11470,13 @@
         <v>320</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>321</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>322</v>
@@ -11463,13 +11493,13 @@
         <v>323</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>324</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>325</v>
@@ -11486,13 +11516,13 @@
         <v>326</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>327</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>328</v>
@@ -11532,13 +11562,13 @@
         <v>332</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>333</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>334</v>
@@ -11555,13 +11585,13 @@
         <v>335</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>336</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>337</v>
@@ -11578,16 +11608,16 @@
         <v>338</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="E18" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>291</v>
@@ -11598,19 +11628,19 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>291</v>
@@ -11621,19 +11651,19 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>291</v>
@@ -11644,19 +11674,19 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>291</v>
@@ -11667,19 +11697,19 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>291</v>
@@ -11690,19 +11720,19 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>291</v>
@@ -11713,16 +11743,16 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>357</v>
@@ -11739,13 +11769,13 @@
         <v>358</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>359</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>360</v>
@@ -11762,13 +11792,13 @@
         <v>361</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>362</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>363</v>
@@ -11785,13 +11815,13 @@
         <v>288</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>364</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>365</v>
@@ -11808,13 +11838,13 @@
         <v>293</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>366</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>367</v>
@@ -11831,13 +11861,13 @@
         <v>296</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>368</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>110</v>
+        <v>54</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>369</v>
@@ -11860,7 +11890,7 @@
         <v>370</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>371</v>
@@ -11900,13 +11930,13 @@
         <v>305</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>374</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>375</v>
@@ -11923,13 +11953,13 @@
         <v>308</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>376</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>377</v>
@@ -11952,7 +11982,7 @@
         <v>378</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>379</v>
@@ -11969,13 +11999,13 @@
         <v>314</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>380</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>381</v>
@@ -11992,13 +12022,13 @@
         <v>317</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>382</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>46</v>
+        <v>116</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>383</v>
@@ -12015,13 +12045,13 @@
         <v>320</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>384</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>385</v>
@@ -12038,13 +12068,13 @@
         <v>323</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>386</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>387</v>
@@ -12061,13 +12091,13 @@
         <v>326</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>388</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>389</v>
@@ -12107,13 +12137,13 @@
         <v>332</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>392</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>393</v>
@@ -12130,13 +12160,13 @@
         <v>335</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>394</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>395</v>
@@ -12153,16 +12183,16 @@
         <v>338</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="E43" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>291</v>
@@ -12173,19 +12203,19 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>291</v>
@@ -12196,19 +12226,19 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>291</v>
@@ -12219,19 +12249,19 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>291</v>
@@ -12242,19 +12272,19 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>291</v>
@@ -12265,19 +12295,19 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>291</v>
@@ -12288,16 +12318,16 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>408</v>
@@ -12314,13 +12344,13 @@
         <v>358</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>409</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>410</v>
@@ -12337,13 +12367,13 @@
         <v>361</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>411</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>412</v>
@@ -12360,13 +12390,13 @@
         <v>288</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>413</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>414</v>
@@ -12383,13 +12413,13 @@
         <v>293</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>415</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>416</v>
@@ -12406,13 +12436,13 @@
         <v>296</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>417</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>110</v>
+        <v>54</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>418</v>
@@ -12435,7 +12465,7 @@
         <v>419</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>420</v>
@@ -12475,13 +12505,13 @@
         <v>305</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>423</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>424</v>
@@ -12498,13 +12528,13 @@
         <v>308</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>425</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>426</v>
@@ -12527,7 +12557,7 @@
         <v>427</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>428</v>
@@ -12544,13 +12574,13 @@
         <v>314</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>429</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>430</v>
@@ -12567,13 +12597,13 @@
         <v>317</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>431</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>46</v>
+        <v>116</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>432</v>
@@ -12590,13 +12620,13 @@
         <v>320</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>433</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>434</v>
@@ -12613,13 +12643,13 @@
         <v>323</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>435</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>436</v>
@@ -12636,13 +12666,13 @@
         <v>326</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>437</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>438</v>
@@ -12682,13 +12712,13 @@
         <v>332</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>441</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>442</v>
@@ -12705,13 +12735,13 @@
         <v>335</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>443</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>444</v>
@@ -12728,16 +12758,16 @@
         <v>338</v>
       </c>
       <c r="B68" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="D68" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="E68" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>291</v>
@@ -12748,19 +12778,19 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>291</v>
@@ -12771,19 +12801,19 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>291</v>
@@ -12794,19 +12824,19 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>291</v>
@@ -12817,19 +12847,19 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>291</v>
@@ -12840,19 +12870,19 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>291</v>
@@ -12863,16 +12893,16 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>457</v>
@@ -12889,13 +12919,13 @@
         <v>358</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>458</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>459</v>
@@ -12912,13 +12942,13 @@
         <v>361</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>460</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>461</v>
@@ -12935,13 +12965,13 @@
         <v>288</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>462</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>463</v>
@@ -12958,13 +12988,13 @@
         <v>293</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>464</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>465</v>
@@ -12981,13 +13011,13 @@
         <v>296</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>466</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>110</v>
+        <v>54</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>467</v>
@@ -13010,7 +13040,7 @@
         <v>468</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>469</v>
@@ -13050,13 +13080,13 @@
         <v>305</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>472</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>473</v>
@@ -13073,13 +13103,13 @@
         <v>308</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>474</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>475</v>
@@ -13102,7 +13132,7 @@
         <v>476</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>477</v>
@@ -13119,13 +13149,13 @@
         <v>314</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>478</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>479</v>
@@ -13142,13 +13172,13 @@
         <v>317</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>480</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>46</v>
+        <v>116</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>481</v>
@@ -13165,13 +13195,13 @@
         <v>320</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>482</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>483</v>
@@ -13188,13 +13218,13 @@
         <v>323</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>484</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>485</v>
@@ -13211,13 +13241,13 @@
         <v>326</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>486</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>487</v>
@@ -13257,13 +13287,13 @@
         <v>332</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>490</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>491</v>
@@ -13280,13 +13310,13 @@
         <v>335</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>492</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>493</v>
@@ -13303,16 +13333,16 @@
         <v>338</v>
       </c>
       <c r="B93" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="D93" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C93" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="E93" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>291</v>
@@ -13323,19 +13353,19 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>291</v>
@@ -13346,19 +13376,19 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>291</v>
@@ -13369,19 +13399,19 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>291</v>
@@ -13392,19 +13422,19 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>291</v>
@@ -13415,19 +13445,19 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>291</v>
@@ -13438,16 +13468,16 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>506</v>
@@ -13464,13 +13494,13 @@
         <v>358</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>507</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>508</v>
@@ -13487,13 +13517,13 @@
         <v>361</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>509</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>510</v>
@@ -13510,13 +13540,13 @@
         <v>288</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>511</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>512</v>
@@ -13533,13 +13563,13 @@
         <v>293</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>513</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>514</v>
@@ -13556,13 +13586,13 @@
         <v>296</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>515</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>110</v>
+        <v>54</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>516</v>
@@ -13585,7 +13615,7 @@
         <v>517</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>518</v>
@@ -13625,13 +13655,13 @@
         <v>305</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>521</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>522</v>
@@ -13648,13 +13678,13 @@
         <v>308</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>523</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>524</v>
@@ -13677,7 +13707,7 @@
         <v>525</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>526</v>
@@ -13694,13 +13724,13 @@
         <v>314</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>527</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>528</v>
@@ -13717,13 +13747,13 @@
         <v>317</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>529</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>46</v>
+        <v>116</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>530</v>
@@ -13740,13 +13770,13 @@
         <v>320</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>531</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>532</v>
@@ -13763,13 +13793,13 @@
         <v>323</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>533</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>534</v>
@@ -13786,13 +13816,13 @@
         <v>326</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>535</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>536</v>
@@ -13832,13 +13862,13 @@
         <v>332</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>539</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>540</v>
@@ -13855,13 +13885,13 @@
         <v>335</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>541</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>542</v>
@@ -13878,16 +13908,16 @@
         <v>338</v>
       </c>
       <c r="B118" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="D118" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C118" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="E118" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>291</v>
@@ -13898,19 +13928,19 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>291</v>
@@ -13921,19 +13951,19 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>291</v>
@@ -13944,19 +13974,19 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>291</v>
@@ -13967,19 +13997,19 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>291</v>
@@ -13990,19 +14020,19 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>291</v>
@@ -14013,16 +14043,16 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>555</v>
@@ -14039,13 +14069,13 @@
         <v>358</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>556</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>557</v>
@@ -14062,13 +14092,13 @@
         <v>361</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>558</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>559</v>
@@ -14085,13 +14115,13 @@
         <v>288</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>560</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>561</v>
@@ -14108,13 +14138,13 @@
         <v>293</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>562</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>563</v>
@@ -14131,13 +14161,13 @@
         <v>296</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>564</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>110</v>
+        <v>54</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>565</v>
@@ -14160,7 +14190,7 @@
         <v>566</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>567</v>
@@ -14200,13 +14230,13 @@
         <v>305</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>570</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>571</v>
@@ -14223,13 +14253,13 @@
         <v>308</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>572</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>573</v>
@@ -14252,7 +14282,7 @@
         <v>574</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>575</v>
@@ -14269,13 +14299,13 @@
         <v>314</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>576</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>577</v>
@@ -14292,13 +14322,13 @@
         <v>317</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>578</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>46</v>
+        <v>116</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>579</v>
@@ -14315,13 +14345,13 @@
         <v>320</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>580</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>581</v>
@@ -14338,13 +14368,13 @@
         <v>323</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>582</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>583</v>
@@ -14361,13 +14391,13 @@
         <v>326</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>584</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>585</v>
@@ -14407,13 +14437,13 @@
         <v>332</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>588</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>589</v>
@@ -14430,13 +14460,13 @@
         <v>335</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>590</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>591</v>
@@ -14453,16 +14483,16 @@
         <v>338</v>
       </c>
       <c r="B143" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="D143" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C143" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="D143" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="E143" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>291</v>
@@ -14473,19 +14503,19 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>291</v>
@@ -14496,19 +14526,19 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>291</v>
@@ -14519,19 +14549,19 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>291</v>
@@ -14542,19 +14572,19 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>291</v>
@@ -14565,19 +14595,19 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>291</v>
@@ -14588,16 +14618,16 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>604</v>
@@ -14614,13 +14644,13 @@
         <v>358</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>605</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>606</v>
@@ -14637,13 +14667,13 @@
         <v>361</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>607</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>608</v>
@@ -14660,13 +14690,13 @@
         <v>288</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>609</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>610</v>
@@ -14683,13 +14713,13 @@
         <v>293</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>611</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>612</v>
@@ -14706,13 +14736,13 @@
         <v>296</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>613</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>110</v>
+        <v>54</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>614</v>
@@ -14735,7 +14765,7 @@
         <v>615</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>616</v>
@@ -14775,13 +14805,13 @@
         <v>305</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>619</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>620</v>
@@ -14798,13 +14828,13 @@
         <v>308</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>621</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>622</v>
@@ -14827,7 +14857,7 @@
         <v>623</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>624</v>
@@ -14844,13 +14874,13 @@
         <v>314</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>625</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>626</v>
@@ -14867,13 +14897,13 @@
         <v>317</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>627</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>46</v>
+        <v>116</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>628</v>
@@ -14890,13 +14920,13 @@
         <v>320</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>629</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>630</v>
@@ -14913,13 +14943,13 @@
         <v>323</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>631</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>632</v>
@@ -14936,13 +14966,13 @@
         <v>326</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>633</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>634</v>
@@ -14982,13 +15012,13 @@
         <v>332</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>637</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>638</v>
@@ -15005,13 +15035,13 @@
         <v>335</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>639</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>640</v>
@@ -15028,16 +15058,16 @@
         <v>338</v>
       </c>
       <c r="B168" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D168" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C168" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="D168" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="E168" s="2" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F168" s="2" t="s">
         <v>291</v>
@@ -15048,19 +15078,19 @@
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F169" s="2" t="s">
         <v>291</v>
@@ -15071,19 +15101,19 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="F170" s="2" t="s">
         <v>291</v>
@@ -15094,19 +15124,19 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F171" s="2" t="s">
         <v>291</v>
@@ -15117,19 +15147,19 @@
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>291</v>
@@ -15140,19 +15170,19 @@
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F173" s="2" t="s">
         <v>291</v>
@@ -15163,16 +15193,16 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>653</v>
@@ -15189,13 +15219,13 @@
         <v>358</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>654</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>655</v>
@@ -15212,13 +15242,13 @@
         <v>361</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>656</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>657</v>
@@ -15241,11 +15271,11 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:DJ152"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="15.73828125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="13.3359375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="15.53515625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="13.25390625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="5.859375" customWidth="true"/>
     <col min="4" max="4" width="5.859375" customWidth="true"/>
     <col min="5" max="5" width="5.859375" customWidth="true"/>
@@ -17243,7 +17273,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="7">
     <mergeCell ref="C1:R1"/>
     <mergeCell ref="S1:AH1"/>
     <mergeCell ref="AI1:AX1"/>
@@ -17262,12 +17292,16 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="44.640625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.08203125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="20.46484375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="17.2734375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="12.34765625" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="6.08984375" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="1.015625" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="12.08984375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="12.73046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17289,26 +17323,31 @@
       <c r="C3" s="1" t="s">
         <v>679</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>681</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>682</v>
       </c>
       <c r="B4" s="2"/>
-      <c r="C4" s="2" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>681</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>680</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-    </row>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2" t="n">
+        <v>-875.0</v>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6"/>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
